--- a/storage/PDS.xlsx
+++ b/storage/PDS.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="533">
   <si>
     <t xml:space="preserve">        </t>
   </si>
@@ -97,6 +97,9 @@
     <t>SURNAME</t>
   </si>
   <si>
+    <t>ADDURU</t>
+  </si>
+  <si>
     <t>SEX</t>
   </si>
   <si>
@@ -109,7 +112,11 @@
     <t>FIRST NAME</t>
   </si>
   <si>
-    <t xml:space="preserve">NAME EXTENSION (JR., SR)                                           </t>
+    <t>JESTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAME EXTENSION (JR., SR)
+</t>
   </si>
   <si>
     <t>Married</t>
@@ -122,6 +129,9 @@
   </si>
   <si>
     <t>MIDDLE NAME</t>
+  </si>
+  <si>
+    <t>CLORES</t>
   </si>
   <si>
     <t>Widow/er</t>
@@ -157,6 +167,9 @@
     </r>
   </si>
   <si>
+    <t>12-02-1999</t>
+  </si>
+  <si>
     <t>16. CITIZENSHIP</t>
   </si>
   <si>
@@ -175,6 +188,9 @@
     <t>PLACE OF BIRTH</t>
   </si>
   <si>
+    <t>TUGUEGARAO CITY</t>
+  </si>
+  <si>
     <t xml:space="preserve">If holder of  dual citizenship, </t>
   </si>
   <si>
@@ -211,6 +227,9 @@
     <t>17. RESIDENTIAL ADDRESS</t>
   </si>
   <si>
+    <t>#88C</t>
+  </si>
+  <si>
     <t>Angola</t>
   </si>
   <si>
@@ -232,6 +251,12 @@
     <t>DUAL</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>ANNAFUNAN WEST</t>
+  </si>
+  <si>
     <t>Argentina</t>
   </si>
   <si>
@@ -259,6 +284,9 @@
     <t>HEIGHT (m)</t>
   </si>
   <si>
+    <t>CAGAYAN</t>
+  </si>
+  <si>
     <t>Australia</t>
   </si>
   <si>
@@ -289,6 +317,9 @@
     <t>BLOOD TYPE</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
     <t>18. PERMANENT ADDRESS</t>
   </si>
   <si>
@@ -304,6 +335,9 @@
     <t xml:space="preserve">UMID ID NO. </t>
   </si>
   <si>
+    <t>GSIS</t>
+  </si>
+  <si>
     <t>Bangladesh</t>
   </si>
   <si>
@@ -337,6 +371,9 @@
     <t>PhilSys Number (PSN):</t>
   </si>
   <si>
+    <t>PHILSYS NO.</t>
+  </si>
+  <si>
     <t>19. TELEPHONE NO.</t>
   </si>
   <si>
@@ -349,6 +386,9 @@
     <t>20. MOBILE NO.</t>
   </si>
   <si>
+    <t>09754112813</t>
+  </si>
+  <si>
     <t>Bhutan</t>
   </si>
   <si>
@@ -358,6 +398,9 @@
     <t>21. E-MAIL ADDRESS (if any)</t>
   </si>
   <si>
+    <t>jesteradduru@gmail.com</t>
+  </si>
+  <si>
     <t>Bolivia</t>
   </si>
   <si>
@@ -385,15 +428,27 @@
     <t xml:space="preserve">  FIRST NAME</t>
   </si>
   <si>
+    <t>GARLAND</t>
+  </si>
+  <si>
     <t xml:space="preserve">NAME EXTENSION (JR., SR)                                     </t>
   </si>
   <si>
+    <t>NERIAH B. ADDURU</t>
+  </si>
+  <si>
+    <t>27/12/2024</t>
+  </si>
+  <si>
     <t>Brazil</t>
   </si>
   <si>
     <t xml:space="preserve">  MIDDLE NAME</t>
   </si>
   <si>
+    <t>BAYSA</t>
+  </si>
+  <si>
     <t>Brunei </t>
   </si>
   <si>
@@ -430,12 +485,19 @@
     <t>Cambodia</t>
   </si>
   <si>
-    <t xml:space="preserve">NAME EXTENSION (JR., SR)                                                  </t>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>NAME EXTENSION (JR., SR)
+SR</t>
   </si>
   <si>
     <t>Cameroon</t>
   </si>
   <si>
+    <t>ALAN</t>
+  </si>
+  <si>
     <t>Canada</t>
   </si>
   <si>
@@ -451,7 +513,13 @@
     <t>Central African Republic</t>
   </si>
   <si>
+    <t>LUZVIMINDA</t>
+  </si>
+  <si>
     <t>Chad</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
   </si>
   <si>
     <t>(Continue on separate sheet if necessary)</t>
@@ -512,12 +580,24 @@
     <t>ELEMENTARY</t>
   </si>
   <si>
+    <t>ANNAFUNAN ELEMENTARY SCHOOL</t>
+  </si>
+  <si>
+    <t>BASIC EDUCATION</t>
+  </si>
+  <si>
     <t>Congo, Republic of the</t>
   </si>
   <si>
     <t>SECONDARY</t>
   </si>
   <si>
+    <t>LINAO NATIONAL HIGH SCHOOL</t>
+  </si>
+  <si>
+    <t>HIGH SCHOOL</t>
+  </si>
+  <si>
     <t>Costa Rica</t>
   </si>
   <si>
@@ -530,10 +610,22 @@
     <t>COLLEGE</t>
   </si>
   <si>
+    <t>CAGAYAN STATE UNIVERSITY - CARIG CAMPUS</t>
+  </si>
+  <si>
+    <t>BACHELOR OF SCIENCE IN INFORMATION TECHNOLOGY</t>
+  </si>
+  <si>
     <t>Croatia</t>
   </si>
   <si>
     <t xml:space="preserve">GRADUATE STUDIES </t>
+  </si>
+  <si>
+    <t>17-SEP-2025</t>
+  </si>
+  <si>
+    <t>19-JAN-1989</t>
   </si>
   <si>
     <t>Cuba</t>
@@ -1056,6 +1148,18 @@
     <t>Valid Until</t>
   </si>
   <si>
+    <t>CAREER SERVICE PROFESSIONAL</t>
+  </si>
+  <si>
+    <t>03/12/2022</t>
+  </si>
+  <si>
+    <t>TUGUEGARAO CITY, CAGAYAN</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">V.  WORK EXPERIENCE </t>
   </si>
   <si>
@@ -1078,6 +1182,81 @@
   </si>
   <si>
     <t>GOV'T SERVICE                                                                                                                                       (Y/ N)</t>
+  </si>
+  <si>
+    <t>01/08/2023</t>
+  </si>
+  <si>
+    <t>TO PRESENT</t>
+  </si>
+  <si>
+    <t>INFORMATION SYSTEMS ANALYST I</t>
+  </si>
+  <si>
+    <t>DEPARTMENT OF ECONOMY, PLANNING, AND DEVELOPMENT</t>
+  </si>
+  <si>
+    <t>PERMANENT</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>03/07/2023</t>
+  </si>
+  <si>
+    <t>21/07/2023</t>
+  </si>
+  <si>
+    <t>DATABASE MANAGEMENT OFFICER</t>
+  </si>
+  <si>
+    <t>PROVINCIAL ENVIRONMENT AND NATURAL RESOURCES OFFICE CAGAYAN</t>
+  </si>
+  <si>
+    <t>CONTRACTUAL</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>17/10/2022</t>
+  </si>
+  <si>
+    <t>30/01/2023</t>
+  </si>
+  <si>
+    <t>DEPARTMENT OF AGRICULTURE RFO2</t>
+  </si>
+  <si>
+    <t>17/01/2022</t>
+  </si>
+  <si>
+    <t>30/09/2022</t>
+  </si>
+  <si>
+    <t>ENGINEERING AIDE - SOFTWARE</t>
+  </si>
+  <si>
+    <t>01/12/2020</t>
+  </si>
+  <si>
+    <t>30/12/2021</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE AIDE IV</t>
+  </si>
+  <si>
+    <t>01/09/2019</t>
+  </si>
+  <si>
+    <t>30/11/2019</t>
+  </si>
+  <si>
+    <t>GRAPHIC ARTIST</t>
+  </si>
+  <si>
+    <t>TRANSFER IT ROBINSONS TUGUEGARAO</t>
   </si>
   <si>
     <t xml:space="preserve">                               CS FORM 212 (Revised 2025), Page 2 of 4</t>
@@ -1144,6 +1323,114 @@
     <t xml:space="preserve"> CONDUCTED/ SPONSORED BY                                                               (Write in full)</t>
   </si>
   <si>
+    <t>THE BITS AND BYTES OF COMPUTER NETWORKING</t>
+  </si>
+  <si>
+    <t>28/05/2026</t>
+  </si>
+  <si>
+    <t>TECHNICAL</t>
+  </si>
+  <si>
+    <t>GOOGLE</t>
+  </si>
+  <si>
+    <t>CLOUD AND DEVOPS BASICS</t>
+  </si>
+  <si>
+    <t>12/12/2025</t>
+  </si>
+  <si>
+    <t>DEPARTMENT OF INFORMATION AND COMMUNICATIONS TECHNOLOGY REGIONAL OFFICE 2</t>
+  </si>
+  <si>
+    <t>CYBER RANGE EXERCISES 2025</t>
+  </si>
+  <si>
+    <t>17/10/2025</t>
+  </si>
+  <si>
+    <t>CLOUD AND NETWORK SERVICE</t>
+  </si>
+  <si>
+    <t>27/05/2025</t>
+  </si>
+  <si>
+    <t>CYBER RANGE EXERCISES 2024</t>
+  </si>
+  <si>
+    <t>28/08/2024</t>
+  </si>
+  <si>
+    <t>ALAY SA BAYAN</t>
+  </si>
+  <si>
+    <t>06/02/2024</t>
+  </si>
+  <si>
+    <t>FOUNDATION</t>
+  </si>
+  <si>
+    <t>CSC REGION 2</t>
+  </si>
+  <si>
+    <t>TECHNICAL SUPPORT FUNDAMENTALS</t>
+  </si>
+  <si>
+    <t>14/03/2023</t>
+  </si>
+  <si>
+    <t>13/03/2023</t>
+  </si>
+  <si>
+    <t>FOUNDATIONS OF USER EXPERIENCE (UX) DESIGN</t>
+  </si>
+  <si>
+    <t>01/03/2023</t>
+  </si>
+  <si>
+    <t>DATA WAREHOUSING AND VISUALIZATION USING MICROSOFT POWER BI TRAINING COURSE</t>
+  </si>
+  <si>
+    <t>31/08/2022</t>
+  </si>
+  <si>
+    <t>02/09/2022</t>
+  </si>
+  <si>
+    <t>DEPARTMENT OF AGRICULTURE REGIONAL FIELD OFFICE 2</t>
+  </si>
+  <si>
+    <t>UI/UX FUNDAMENTALS</t>
+  </si>
+  <si>
+    <t>22/06/2022</t>
+  </si>
+  <si>
+    <t>OPEN SOURCE INTELLIGENCE (OSINT)</t>
+  </si>
+  <si>
+    <t>20/06/2022</t>
+  </si>
+  <si>
+    <t>06/06/2022</t>
+  </si>
+  <si>
+    <t>BASIC COMPUTER NETWORKING</t>
+  </si>
+  <si>
+    <t>09/06/2022</t>
+  </si>
+  <si>
+    <t>BASIC COMPUTER HARDWARE TROUBLESHOOTING AND MAINTENANCE</t>
+  </si>
+  <si>
+    <t>07/03/2022</t>
+  </si>
+  <si>
+    <t>11/03/2022</t>
+  </si>
+  <si>
     <t>VIII.  OTHER INFORMATION</t>
   </si>
   <si>
@@ -1163,6 +1450,27 @@
   </si>
   <si>
     <t>MEMBERSHIP IN ASSOCIATION/ORGANIZATION                                                                                         (Write in full)</t>
+  </si>
+  <si>
+    <t>PLAYING GUITAR AND DRUMS</t>
+  </si>
+  <si>
+    <t>2024 ROOKIE OF THE YEAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GAMING</t>
+  </si>
+  <si>
+    <t>2024 MALASAKIT AWARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> COOKING</t>
+  </si>
+  <si>
+    <t>2025 COMMUNITY SERVICE AWARD</t>
+  </si>
+  <si>
+    <t>2025 MALASAKIT AWARD</t>
   </si>
   <si>
     <t xml:space="preserve"> CS FORM 212 (Revised 2025), Page 3 of 4</t>
@@ -1314,6 +1622,27 @@
   </si>
   <si>
     <t>CONTACT NO. AND/OR EMAIL</t>
+  </si>
+  <si>
+    <t>ANTHONY JAMES C. ARTICULO</t>
+  </si>
+  <si>
+    <t>DEPDEV REGION 2</t>
+  </si>
+  <si>
+    <t>09173153299</t>
+  </si>
+  <si>
+    <t>RITCHIE S. AVENA</t>
+  </si>
+  <si>
+    <t>09452468132</t>
+  </si>
+  <si>
+    <t>ELY MAE IBANEZ</t>
+  </si>
+  <si>
+    <t>09056532280</t>
   </si>
   <si>
     <t>42.</t>
@@ -1391,13 +1720,22 @@
     <t xml:space="preserve">Government Issued ID: </t>
   </si>
   <si>
+    <t>DRIVER LICENSE</t>
+  </si>
+  <si>
     <t xml:space="preserve">ID/License/Passport No.: </t>
   </si>
   <si>
+    <t>B04-20-003648</t>
+  </si>
+  <si>
     <t>Signature (Sign inside the box)</t>
   </si>
   <si>
     <t>Date/Place of Issuance:</t>
+  </si>
+  <si>
+    <t>LTO TUGUEGARAO</t>
   </si>
   <si>
     <t>Date Accomplished</t>
@@ -10274,7 +10612,9 @@
         <v>10</v>
       </c>
       <c r="C10" s="288"/>
-      <c r="D10" s="335"/>
+      <c r="D10" s="335" t="s">
+        <v>11</v>
+      </c>
       <c r="E10" s="335"/>
       <c r="F10" s="335"/>
       <c r="G10" s="335"/>
@@ -10289,25 +10629,27 @@
       <c r="P10" s="227"/>
       <c r="Q10" s="228"/>
       <c r="R10" s="228" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S10" s="228" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T10" s="228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" s="228"/>
     </row>
     <row r="11" spans="1:21" customHeight="1" ht="22.5">
       <c r="A11" s="138" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="344" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="345"/>
-      <c r="D11" s="360"/>
+      <c r="D11" s="360" t="s">
+        <v>16</v>
+      </c>
       <c r="E11" s="259"/>
       <c r="F11" s="259"/>
       <c r="G11" s="259"/>
@@ -10316,20 +10658,20 @@
       <c r="J11" s="259"/>
       <c r="K11" s="361"/>
       <c r="L11" s="298" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M11" s="299"/>
       <c r="N11" s="300"/>
       <c r="O11" s="228"/>
       <c r="P11" s="228" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q11" s="229" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R11" s="228"/>
       <c r="S11" s="228" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T11" s="228" t="b">
         <v>0</v>
@@ -10339,10 +10681,12 @@
     <row r="12" spans="1:21" customHeight="1" ht="21.75">
       <c r="A12" s="139"/>
       <c r="B12" s="346" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" s="347"/>
-      <c r="D12" s="362"/>
+      <c r="D12" s="362" t="s">
+        <v>22</v>
+      </c>
       <c r="E12" s="363"/>
       <c r="F12" s="363"/>
       <c r="G12" s="363"/>
@@ -10355,16 +10699,16 @@
       <c r="N12" s="364"/>
       <c r="O12" s="228"/>
       <c r="P12" s="228" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q12" s="230" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R12" s="228" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="S12" s="228" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T12" s="228" t="b">
         <v>0</v>
@@ -10373,17 +10717,19 @@
     </row>
     <row r="13" spans="1:21" customHeight="1" ht="24">
       <c r="A13" s="198" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B13" s="287" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C13" s="288"/>
-      <c r="D13" s="289"/>
+      <c r="D13" s="289" t="s">
+        <v>29</v>
+      </c>
       <c r="E13" s="289"/>
       <c r="F13" s="290"/>
       <c r="G13" s="75" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H13" s="119"/>
       <c r="I13" s="119"/>
@@ -10394,14 +10740,14 @@
       <c r="N13" s="303"/>
       <c r="O13" s="228"/>
       <c r="P13" s="228" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q13" s="230" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="R13" s="228"/>
       <c r="S13" s="228" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="T13" s="228" t="b">
         <v>0</v>
@@ -10428,46 +10774,48 @@
       <c r="Q14" s="230"/>
       <c r="R14" s="228"/>
       <c r="S14" s="228" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T14" s="228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" s="228"/>
     </row>
     <row r="15" spans="1:21" customHeight="1" ht="24.75">
       <c r="A15" s="140" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B15" s="70" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C15" s="70"/>
-      <c r="D15" s="257"/>
+      <c r="D15" s="257" t="s">
+        <v>36</v>
+      </c>
       <c r="E15" s="257"/>
       <c r="F15" s="258"/>
       <c r="G15" s="294" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H15" s="295"/>
       <c r="I15" s="295"/>
       <c r="J15" s="120"/>
       <c r="K15" s="121"/>
       <c r="L15" s="275" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M15" s="275"/>
       <c r="N15" s="276"/>
       <c r="O15" s="228"/>
       <c r="P15" s="228" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="Q15" s="230" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="R15" s="228"/>
       <c r="S15" s="228" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="T15" s="228" t="b">
         <v>0</v>
@@ -10476,17 +10824,17 @@
     </row>
     <row r="16" spans="1:21" customHeight="1" ht="24.75">
       <c r="A16" s="141" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B16" s="220" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C16" s="71"/>
       <c r="D16" s="337"/>
       <c r="E16" s="337"/>
       <c r="F16" s="338"/>
       <c r="G16" s="291" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H16" s="292"/>
       <c r="I16" s="293"/>
@@ -10497,14 +10845,14 @@
       <c r="N16" s="280"/>
       <c r="O16" s="228"/>
       <c r="P16" s="228" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q16" s="230" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="R16" s="228"/>
       <c r="S16" s="228" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="T16" s="228" t="b">
         <v>0</v>
@@ -10516,35 +10864,39 @@
         <v>6</v>
       </c>
       <c r="B17" s="327" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C17" s="328"/>
       <c r="D17" s="325"/>
       <c r="E17" s="325"/>
       <c r="F17" s="325"/>
       <c r="G17" s="76" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H17" s="77"/>
-      <c r="I17" s="260"/>
+      <c r="I17" s="260" t="s">
+        <v>49</v>
+      </c>
       <c r="J17" s="261"/>
       <c r="K17" s="261"/>
-      <c r="L17" s="261"/>
+      <c r="L17" s="261" t="s">
+        <v>11</v>
+      </c>
       <c r="M17" s="261"/>
       <c r="N17" s="277"/>
       <c r="O17" s="228"/>
       <c r="P17" s="228"/>
       <c r="Q17" s="230" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="R17" s="228" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="S17" s="228" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="T17" s="228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" s="228"/>
     </row>
@@ -10558,23 +10910,23 @@
       <c r="G18" s="127"/>
       <c r="H18" s="78"/>
       <c r="I18" s="272" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J18" s="273"/>
       <c r="K18" s="273"/>
       <c r="L18" s="273" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M18" s="273"/>
       <c r="N18" s="274"/>
       <c r="O18" s="228"/>
       <c r="P18" s="228"/>
       <c r="Q18" s="230" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="R18" s="228"/>
       <c r="S18" s="228" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="T18" s="228" t="b">
         <v>0</v>
@@ -10590,16 +10942,20 @@
       <c r="F19" s="131"/>
       <c r="G19" s="127"/>
       <c r="H19" s="78"/>
-      <c r="I19" s="304"/>
+      <c r="I19" s="304" t="s">
+        <v>57</v>
+      </c>
       <c r="J19" s="305"/>
       <c r="K19" s="305"/>
-      <c r="L19" s="308"/>
+      <c r="L19" s="308" t="s">
+        <v>58</v>
+      </c>
       <c r="M19" s="305"/>
       <c r="N19" s="309"/>
       <c r="O19" s="228"/>
       <c r="P19" s="228"/>
       <c r="Q19" s="230" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="R19" s="228"/>
       <c r="S19" s="228"/>
@@ -10624,11 +10980,11 @@
       <c r="O20" s="228"/>
       <c r="P20" s="228"/>
       <c r="Q20" s="230" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="R20" s="228"/>
       <c r="S20" s="228" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="T20" s="228" t="b">
         <v>0</v>
@@ -10645,23 +11001,23 @@
       <c r="G21" s="125"/>
       <c r="H21" s="130"/>
       <c r="I21" s="311" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J21" s="312"/>
       <c r="K21" s="312"/>
       <c r="L21" s="385" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="M21" s="386"/>
       <c r="N21" s="387"/>
       <c r="O21" s="228"/>
       <c r="P21" s="228"/>
       <c r="Q21" s="230" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="R21" s="228"/>
       <c r="S21" s="228" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="T21" s="228" t="b">
         <v>0</v>
@@ -10670,27 +11026,33 @@
     </row>
     <row r="22" spans="1:21" customHeight="1" ht="15.75">
       <c r="A22" s="323" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B22" s="252" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C22" s="253"/>
-      <c r="D22" s="377"/>
+      <c r="D22" s="377">
+        <v>1.71</v>
+      </c>
       <c r="E22" s="377"/>
       <c r="F22" s="377"/>
       <c r="G22" s="125"/>
       <c r="H22" s="130"/>
-      <c r="I22" s="260"/>
+      <c r="I22" s="260" t="s">
+        <v>36</v>
+      </c>
       <c r="J22" s="261"/>
       <c r="K22" s="261"/>
-      <c r="L22" s="261"/>
+      <c r="L22" s="261" t="s">
+        <v>68</v>
+      </c>
       <c r="M22" s="261"/>
       <c r="N22" s="277"/>
       <c r="O22" s="228"/>
       <c r="P22" s="228"/>
       <c r="Q22" s="230" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="R22" s="228"/>
       <c r="S22" s="228"/>
@@ -10707,19 +11069,19 @@
       <c r="G23" s="125"/>
       <c r="H23" s="130"/>
       <c r="I23" s="390" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J23" s="391"/>
       <c r="K23" s="391"/>
       <c r="L23" s="388" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="M23" s="388"/>
       <c r="N23" s="389"/>
       <c r="O23" s="228"/>
       <c r="P23" s="228"/>
       <c r="Q23" s="230" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="R23" s="228"/>
       <c r="S23" s="228"/>
@@ -10728,20 +11090,24 @@
     </row>
     <row r="24" spans="1:21" customHeight="1" ht="22.5">
       <c r="A24" s="138" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B24" s="350" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C24" s="351"/>
-      <c r="D24" s="259"/>
+      <c r="D24" s="259">
+        <v>68</v>
+      </c>
       <c r="E24" s="259"/>
       <c r="F24" s="259"/>
       <c r="G24" s="265" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H24" s="266"/>
-      <c r="I24" s="353"/>
+      <c r="I24" s="353">
+        <v>3500</v>
+      </c>
       <c r="J24" s="354"/>
       <c r="K24" s="354"/>
       <c r="L24" s="354"/>
@@ -10750,7 +11116,7 @@
       <c r="O24" s="228"/>
       <c r="P24" s="228"/>
       <c r="Q24" s="230" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="R24" s="228"/>
       <c r="S24" s="228"/>
@@ -10759,27 +11125,33 @@
     </row>
     <row r="25" spans="1:21" customHeight="1" ht="15.75">
       <c r="A25" s="313" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B25" s="252" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C25" s="253"/>
-      <c r="D25" s="271"/>
+      <c r="D25" s="271" t="s">
+        <v>79</v>
+      </c>
       <c r="E25" s="271"/>
       <c r="F25" s="271"/>
       <c r="G25" s="83" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H25" s="72"/>
-      <c r="I25" s="260"/>
+      <c r="I25" s="260" t="s">
+        <v>49</v>
+      </c>
       <c r="J25" s="261"/>
       <c r="K25" s="261"/>
-      <c r="L25" s="261"/>
+      <c r="L25" s="261" t="s">
+        <v>11</v>
+      </c>
       <c r="M25" s="261"/>
       <c r="N25" s="277"/>
       <c r="Q25" s="3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:21" customHeight="1" ht="9">
@@ -10792,40 +11164,46 @@
       <c r="G26" s="125"/>
       <c r="H26" s="130"/>
       <c r="I26" s="272" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J26" s="273"/>
       <c r="K26" s="273"/>
       <c r="L26" s="273" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M26" s="273"/>
       <c r="N26" s="274"/>
       <c r="Q26" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:21" customHeight="1" ht="15.75">
       <c r="A27" s="313" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B27" s="380" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C27" s="253"/>
-      <c r="D27" s="271"/>
+      <c r="D27" s="271" t="s">
+        <v>85</v>
+      </c>
       <c r="E27" s="271"/>
       <c r="F27" s="271"/>
       <c r="G27" s="127"/>
       <c r="H27" s="78"/>
-      <c r="I27" s="260"/>
+      <c r="I27" s="260" t="s">
+        <v>57</v>
+      </c>
       <c r="J27" s="261"/>
       <c r="K27" s="261"/>
-      <c r="L27" s="261"/>
+      <c r="L27" s="261" t="s">
+        <v>58</v>
+      </c>
       <c r="M27" s="261"/>
       <c r="N27" s="277"/>
       <c r="Q27" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:21" customHeight="1" ht="9">
@@ -10838,40 +11216,46 @@
       <c r="G28" s="127"/>
       <c r="H28" s="78"/>
       <c r="I28" s="381" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J28" s="382"/>
       <c r="K28" s="382"/>
       <c r="L28" s="383" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="M28" s="382"/>
       <c r="N28" s="384"/>
       <c r="Q28" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:21" customHeight="1" ht="15.75">
       <c r="A29" s="313" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B29" s="252" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C29" s="253"/>
-      <c r="D29" s="316"/>
+      <c r="D29" s="316">
+        <v>0</v>
+      </c>
       <c r="E29" s="271"/>
       <c r="F29" s="317"/>
       <c r="G29" s="127"/>
       <c r="H29" s="133"/>
-      <c r="I29" s="284"/>
+      <c r="I29" s="284" t="s">
+        <v>36</v>
+      </c>
       <c r="J29" s="285"/>
       <c r="K29" s="285"/>
-      <c r="L29" s="285"/>
+      <c r="L29" s="285" t="s">
+        <v>68</v>
+      </c>
       <c r="M29" s="285"/>
       <c r="N29" s="286"/>
       <c r="Q29" s="3" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:21" customHeight="1" ht="9.75">
@@ -10884,118 +11268,134 @@
       <c r="G30" s="127"/>
       <c r="H30" s="133"/>
       <c r="I30" s="296" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J30" s="296"/>
       <c r="K30" s="296"/>
       <c r="L30" s="296" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="M30" s="296"/>
       <c r="N30" s="297"/>
       <c r="Q30" s="3" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:21" customHeight="1" ht="24.75">
       <c r="A31" s="140" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B31" s="70" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C31" s="71"/>
-      <c r="D31" s="271"/>
+      <c r="D31" s="271">
+        <v>0</v>
+      </c>
       <c r="E31" s="271"/>
       <c r="F31" s="271"/>
       <c r="G31" s="265" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H31" s="266"/>
-      <c r="I31" s="416"/>
+      <c r="I31" s="416">
+        <v>3500</v>
+      </c>
       <c r="J31" s="417"/>
       <c r="K31" s="417"/>
       <c r="L31" s="417"/>
       <c r="M31" s="417"/>
       <c r="N31" s="418"/>
       <c r="Q31" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:21" customHeight="1" ht="24.75">
       <c r="A32" s="138" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B32" s="220" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C32" s="71"/>
-      <c r="D32" s="259"/>
+      <c r="D32" s="259" t="s">
+        <v>97</v>
+      </c>
       <c r="E32" s="259"/>
       <c r="F32" s="259"/>
       <c r="G32" s="124" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H32" s="128"/>
-      <c r="I32" s="262"/>
+      <c r="I32" s="262" t="s">
+        <v>57</v>
+      </c>
       <c r="J32" s="263"/>
       <c r="K32" s="263"/>
       <c r="L32" s="263"/>
       <c r="M32" s="263"/>
       <c r="N32" s="264"/>
       <c r="Q32" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:21" customHeight="1" ht="24.75">
       <c r="A33" s="349" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B33" s="350"/>
       <c r="C33" s="351"/>
-      <c r="D33" s="352"/>
+      <c r="D33" s="352">
+        <v>0</v>
+      </c>
       <c r="E33" s="352"/>
       <c r="F33" s="352"/>
       <c r="G33" s="167" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H33" s="126"/>
-      <c r="I33" s="262"/>
+      <c r="I33" s="262" t="s">
+        <v>102</v>
+      </c>
       <c r="J33" s="263"/>
       <c r="K33" s="263"/>
       <c r="L33" s="263"/>
       <c r="M33" s="263"/>
       <c r="N33" s="264"/>
       <c r="Q33" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:21" customHeight="1" ht="24.75">
       <c r="A34" s="143" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B34" s="183"/>
       <c r="C34" s="129"/>
-      <c r="D34" s="271"/>
+      <c r="D34" s="271">
+        <v>0</v>
+      </c>
       <c r="E34" s="271"/>
       <c r="F34" s="271"/>
       <c r="G34" s="83" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H34" s="72"/>
-      <c r="I34" s="254"/>
+      <c r="I34" s="254" t="s">
+        <v>106</v>
+      </c>
       <c r="J34" s="255"/>
       <c r="K34" s="255"/>
       <c r="L34" s="255"/>
       <c r="M34" s="255"/>
       <c r="N34" s="256"/>
       <c r="Q34" s="3" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:21" customHeight="1" ht="16.5">
       <c r="A35" s="174" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B35" s="175"/>
       <c r="C35" s="175"/>
@@ -11011,66 +11411,78 @@
       <c r="M35" s="175"/>
       <c r="N35" s="176"/>
       <c r="Q35" s="3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:21" customHeight="1" ht="21">
       <c r="A36" s="75" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B36" s="186" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C36" s="187"/>
-      <c r="D36" s="281"/>
+      <c r="D36" s="281" t="s">
+        <v>11</v>
+      </c>
       <c r="E36" s="282"/>
       <c r="F36" s="282"/>
-      <c r="G36" s="282"/>
+      <c r="G36" s="282" t="s">
+        <v>57</v>
+      </c>
       <c r="H36" s="283"/>
       <c r="I36" s="267" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="J36" s="267"/>
       <c r="K36" s="267"/>
       <c r="L36" s="268"/>
       <c r="M36" s="269" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="N36" s="270"/>
       <c r="Q36" s="3" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:21" customHeight="1" ht="21">
       <c r="A37" s="125"/>
       <c r="B37" s="78" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="C37" s="133"/>
-      <c r="D37" s="240"/>
+      <c r="D37" s="240" t="s">
+        <v>116</v>
+      </c>
       <c r="E37" s="241"/>
       <c r="F37" s="242"/>
       <c r="G37" s="348" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="H37" s="348"/>
-      <c r="I37" s="243"/>
+      <c r="I37" s="243" t="s">
+        <v>118</v>
+      </c>
       <c r="J37" s="243"/>
       <c r="K37" s="243"/>
       <c r="L37" s="244"/>
-      <c r="M37" s="250"/>
+      <c r="M37" s="250" t="s">
+        <v>119</v>
+      </c>
       <c r="N37" s="251"/>
       <c r="Q37" s="3" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:21" customHeight="1" ht="21">
       <c r="A38" s="144"/>
       <c r="B38" s="179" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C38" s="178"/>
-      <c r="D38" s="240"/>
+      <c r="D38" s="240" t="s">
+        <v>122</v>
+      </c>
       <c r="E38" s="241"/>
       <c r="F38" s="241"/>
       <c r="G38" s="241"/>
@@ -11082,16 +11494,18 @@
       <c r="M38" s="250"/>
       <c r="N38" s="251"/>
       <c r="Q38" s="3" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:21" customHeight="1" ht="21">
       <c r="A39" s="145"/>
       <c r="B39" s="70" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="C39" s="71"/>
-      <c r="D39" s="240"/>
+      <c r="D39" s="240" t="s">
+        <v>57</v>
+      </c>
       <c r="E39" s="241"/>
       <c r="F39" s="241"/>
       <c r="G39" s="241"/>
@@ -11103,16 +11517,18 @@
       <c r="M39" s="250"/>
       <c r="N39" s="251"/>
       <c r="Q39" s="3" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:21" customHeight="1" ht="21">
       <c r="A40" s="145"/>
       <c r="B40" s="70" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="C40" s="71"/>
-      <c r="D40" s="240"/>
+      <c r="D40" s="240" t="s">
+        <v>57</v>
+      </c>
       <c r="E40" s="241"/>
       <c r="F40" s="241"/>
       <c r="G40" s="241"/>
@@ -11124,16 +11540,18 @@
       <c r="M40" s="250"/>
       <c r="N40" s="251"/>
       <c r="Q40" s="3" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:21" customHeight="1" ht="21">
       <c r="A41" s="145"/>
       <c r="B41" s="70" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C41" s="71"/>
-      <c r="D41" s="240"/>
+      <c r="D41" s="240" t="s">
+        <v>57</v>
+      </c>
       <c r="E41" s="241"/>
       <c r="F41" s="241"/>
       <c r="G41" s="241"/>
@@ -11145,16 +11563,18 @@
       <c r="M41" s="250"/>
       <c r="N41" s="251"/>
       <c r="Q41" s="3" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:21" customHeight="1" ht="21">
       <c r="A42" s="76"/>
       <c r="B42" s="77" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C42" s="110"/>
-      <c r="D42" s="240"/>
+      <c r="D42" s="240" t="s">
+        <v>57</v>
+      </c>
       <c r="E42" s="241"/>
       <c r="F42" s="241"/>
       <c r="G42" s="241"/>
@@ -11166,18 +11586,20 @@
       <c r="M42" s="250"/>
       <c r="N42" s="251"/>
       <c r="Q42" s="3" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:21" customHeight="1" ht="21">
       <c r="A43" s="177" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B43" s="184" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C43" s="77"/>
-      <c r="D43" s="240"/>
+      <c r="D43" s="240" t="s">
+        <v>11</v>
+      </c>
       <c r="E43" s="241"/>
       <c r="F43" s="241"/>
       <c r="G43" s="241"/>
@@ -11189,20 +11611,22 @@
       <c r="M43" s="250"/>
       <c r="N43" s="251"/>
       <c r="Q43" s="3" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:21" customHeight="1" ht="21">
       <c r="A44" s="125"/>
       <c r="B44" s="130" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C44" s="130"/>
-      <c r="D44" s="240"/>
+      <c r="D44" s="240" t="s">
+        <v>135</v>
+      </c>
       <c r="E44" s="241"/>
       <c r="F44" s="242"/>
       <c r="G44" s="348" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="H44" s="348"/>
       <c r="I44" s="243"/>
@@ -11212,16 +11636,18 @@
       <c r="M44" s="250"/>
       <c r="N44" s="251"/>
       <c r="Q44" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:21" customHeight="1" ht="21">
       <c r="A45" s="144"/>
       <c r="B45" s="172" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C45" s="172"/>
-      <c r="D45" s="240"/>
+      <c r="D45" s="240" t="s">
+        <v>138</v>
+      </c>
       <c r="E45" s="241"/>
       <c r="F45" s="241"/>
       <c r="G45" s="241"/>
@@ -11233,15 +11659,15 @@
       <c r="M45" s="250"/>
       <c r="N45" s="251"/>
       <c r="Q45" s="3" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:21" customHeight="1" ht="21">
       <c r="A46" s="125" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="B46" s="252" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C46" s="252"/>
       <c r="D46" s="252"/>
@@ -11256,7 +11682,7 @@
       <c r="M46" s="250"/>
       <c r="N46" s="251"/>
       <c r="Q46" s="3" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:21" customHeight="1" ht="21">
@@ -11265,7 +11691,9 @@
         <v>10</v>
       </c>
       <c r="C47" s="130"/>
-      <c r="D47" s="436"/>
+      <c r="D47" s="436" t="s">
+        <v>22</v>
+      </c>
       <c r="E47" s="437"/>
       <c r="F47" s="437"/>
       <c r="G47" s="437"/>
@@ -11277,16 +11705,18 @@
       <c r="M47" s="250"/>
       <c r="N47" s="251"/>
       <c r="Q47" s="3" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:21" customHeight="1" ht="21">
       <c r="A48" s="125"/>
       <c r="B48" s="130" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="130"/>
-      <c r="D48" s="436"/>
+      <c r="D48" s="436" t="s">
+        <v>144</v>
+      </c>
       <c r="E48" s="437"/>
       <c r="F48" s="437"/>
       <c r="G48" s="437"/>
@@ -11298,22 +11728,24 @@
       <c r="M48" s="250"/>
       <c r="N48" s="251"/>
       <c r="Q48" s="3" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:21" customHeight="1" ht="21">
       <c r="A49" s="146"/>
       <c r="B49" s="173" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C49" s="173"/>
-      <c r="D49" s="247"/>
+      <c r="D49" s="247" t="s">
+        <v>146</v>
+      </c>
       <c r="E49" s="248"/>
       <c r="F49" s="248"/>
       <c r="G49" s="248"/>
       <c r="H49" s="249"/>
       <c r="I49" s="245" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="J49" s="245"/>
       <c r="K49" s="245"/>
@@ -11321,12 +11753,12 @@
       <c r="M49" s="245"/>
       <c r="N49" s="246"/>
       <c r="Q49" s="3" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:21" customHeight="1" ht="15.75">
       <c r="A50" s="147" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="B50" s="147"/>
       <c r="C50" s="73"/>
@@ -11336,7 +11768,7 @@
       <c r="G50" s="74"/>
       <c r="H50" s="74"/>
       <c r="I50" s="339" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="J50" s="339"/>
       <c r="K50" s="339"/>
@@ -11344,42 +11776,42 @@
       <c r="M50" s="339"/>
       <c r="N50" s="340"/>
       <c r="Q50" s="3" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:21" customHeight="1" ht="14.25">
       <c r="A51" s="331" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="B51" s="401" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C51" s="401"/>
       <c r="D51" s="404" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E51" s="405"/>
       <c r="F51" s="406"/>
       <c r="G51" s="404" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="H51" s="405"/>
       <c r="I51" s="439"/>
       <c r="J51" s="356" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="K51" s="357"/>
       <c r="L51" s="431" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="M51" s="333" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="N51" s="238" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:21" customHeight="1" ht="19.5">
@@ -11398,7 +11830,7 @@
       <c r="M52" s="333"/>
       <c r="N52" s="238"/>
       <c r="Q52" s="3" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="1:21" customHeight="1" ht="14.25">
@@ -11412,10 +11844,10 @@
       <c r="H53" s="411"/>
       <c r="I53" s="441"/>
       <c r="J53" s="79" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="K53" s="80" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="L53" s="432"/>
       <c r="M53" s="334"/>
@@ -11423,55 +11855,75 @@
       <c r="O53" s="81"/>
       <c r="P53" s="81"/>
       <c r="Q53" s="3" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:21" customHeight="1" ht="28.5">
       <c r="A54" s="188"/>
       <c r="B54" s="189" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="C54" s="189"/>
-      <c r="D54" s="262"/>
+      <c r="D54" s="262" t="s">
+        <v>166</v>
+      </c>
       <c r="E54" s="263"/>
       <c r="F54" s="412"/>
-      <c r="G54" s="433"/>
+      <c r="G54" s="433" t="s">
+        <v>167</v>
+      </c>
       <c r="H54" s="434"/>
       <c r="I54" s="435"/>
-      <c r="J54" s="685"/>
-      <c r="K54" s="686"/>
+      <c r="J54" s="685">
+        <v>2005</v>
+      </c>
+      <c r="K54" s="686">
+        <v>2011</v>
+      </c>
       <c r="L54" s="687"/>
-      <c r="M54" s="688"/>
+      <c r="M54" s="688">
+        <v>2011</v>
+      </c>
       <c r="N54" s="689"/>
       <c r="Q54" s="3" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:21" customHeight="1" ht="28.5">
       <c r="A55" s="188"/>
       <c r="B55" s="189" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="C55" s="189"/>
-      <c r="D55" s="262"/>
+      <c r="D55" s="262" t="s">
+        <v>170</v>
+      </c>
       <c r="E55" s="263"/>
       <c r="F55" s="412"/>
-      <c r="G55" s="433"/>
+      <c r="G55" s="433" t="s">
+        <v>171</v>
+      </c>
       <c r="H55" s="434"/>
       <c r="I55" s="435"/>
-      <c r="J55" s="685"/>
-      <c r="K55" s="686"/>
+      <c r="J55" s="685">
+        <v>2011</v>
+      </c>
+      <c r="K55" s="686">
+        <v>2015</v>
+      </c>
       <c r="L55" s="690"/>
-      <c r="M55" s="691"/>
+      <c r="M55" s="691">
+        <v>2015</v>
+      </c>
       <c r="N55" s="689"/>
       <c r="Q55" s="3" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:21" customHeight="1" ht="28.5">
       <c r="A56" s="188"/>
       <c r="B56" s="189" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C56" s="189"/>
       <c r="D56" s="262"/>
@@ -11486,54 +11938,74 @@
       <c r="M56" s="688"/>
       <c r="N56" s="689"/>
       <c r="Q56" s="3" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:21" customHeight="1" ht="28.5">
       <c r="A57" s="188"/>
       <c r="B57" s="189" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="C57" s="189"/>
-      <c r="D57" s="262"/>
+      <c r="D57" s="262" t="s">
+        <v>176</v>
+      </c>
       <c r="E57" s="263"/>
       <c r="F57" s="412"/>
-      <c r="G57" s="395"/>
+      <c r="G57" s="395" t="s">
+        <v>177</v>
+      </c>
       <c r="H57" s="396"/>
       <c r="I57" s="397"/>
-      <c r="J57" s="685"/>
-      <c r="K57" s="686"/>
+      <c r="J57" s="685">
+        <v>2015</v>
+      </c>
+      <c r="K57" s="686">
+        <v>2019</v>
+      </c>
       <c r="L57" s="687"/>
-      <c r="M57" s="691"/>
+      <c r="M57" s="691">
+        <v>2019</v>
+      </c>
       <c r="N57" s="689"/>
       <c r="Q57" s="3" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58" spans="1:21" customHeight="1" ht="28.5">
       <c r="A58" s="190"/>
       <c r="B58" s="191" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="C58" s="191"/>
-      <c r="D58" s="413"/>
+      <c r="D58" s="413" t="s">
+        <v>180</v>
+      </c>
       <c r="E58" s="414"/>
       <c r="F58" s="415"/>
-      <c r="G58" s="398"/>
+      <c r="G58" s="398" t="s">
+        <v>181</v>
+      </c>
       <c r="H58" s="399"/>
       <c r="I58" s="400"/>
-      <c r="J58" s="692"/>
-      <c r="K58" s="693"/>
+      <c r="J58" s="692">
+        <v>93</v>
+      </c>
+      <c r="K58" s="693">
+        <v>99</v>
+      </c>
       <c r="L58" s="694"/>
-      <c r="M58" s="695"/>
+      <c r="M58" s="695">
+        <v>74</v>
+      </c>
       <c r="N58" s="689"/>
       <c r="Q58" s="3" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
     </row>
     <row r="59" spans="1:21" customHeight="1" ht="12">
       <c r="A59" s="423" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B59" s="424"/>
       <c r="C59" s="424"/>
@@ -11549,17 +12021,17 @@
       <c r="M59" s="424"/>
       <c r="N59" s="425"/>
       <c r="Q59" s="3" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
     </row>
     <row r="60" spans="1:21" customHeight="1" ht="27.75">
       <c r="A60" s="420" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="B60" s="421"/>
       <c r="C60" s="422"/>
       <c r="D60" s="426" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E60" s="427"/>
       <c r="F60" s="427"/>
@@ -11567,22 +12039,22 @@
       <c r="H60" s="427"/>
       <c r="I60" s="428"/>
       <c r="J60" s="429" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="K60" s="430"/>
       <c r="L60" s="696">
         <f>NOW()</f>
-        <v>46200.595543981</v>
+        <v>46302.639039352</v>
       </c>
       <c r="M60" s="697"/>
       <c r="N60" s="698"/>
       <c r="Q60" s="3" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61" spans="1:21" customHeight="1" ht="12" s="117" customFormat="1">
       <c r="A61" s="419" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="B61" s="419"/>
       <c r="C61" s="419"/>
@@ -11598,7 +12070,7 @@
       <c r="M61" s="419"/>
       <c r="N61" s="419"/>
       <c r="Q61" s="203" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
     </row>
     <row r="62" spans="1:21" customHeight="1" ht="13.8">
@@ -11617,7 +12089,7 @@
       <c r="M62" s="82"/>
       <c r="N62" s="82"/>
       <c r="Q62" s="3" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:21" customHeight="1" ht="13.8">
@@ -11636,7 +12108,7 @@
       <c r="M63" s="82"/>
       <c r="N63" s="82"/>
       <c r="Q63" s="3" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
     </row>
     <row r="64" spans="1:21" customHeight="1" ht="27.6">
@@ -11655,7 +12127,7 @@
       <c r="M64" s="82"/>
       <c r="N64" s="82"/>
       <c r="Q64" s="3" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65" spans="1:21" customHeight="1" ht="13.8">
@@ -11674,7 +12146,7 @@
       <c r="M65" s="82"/>
       <c r="N65" s="82"/>
       <c r="Q65" s="3" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66" spans="1:21" customHeight="1" ht="13.8">
@@ -11693,7 +12165,7 @@
       <c r="M66" s="82"/>
       <c r="N66" s="82"/>
       <c r="Q66" s="3" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
     </row>
     <row r="67" spans="1:21" customHeight="1" ht="13.8">
@@ -11712,7 +12184,7 @@
       <c r="M67" s="82"/>
       <c r="N67" s="82"/>
       <c r="Q67" s="3" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
     </row>
     <row r="68" spans="1:21" customHeight="1" ht="13.8">
@@ -11731,7 +12203,7 @@
       <c r="M68" s="82"/>
       <c r="N68" s="82"/>
       <c r="Q68" s="3" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69" spans="1:21" customHeight="1" ht="27.6">
@@ -11750,7 +12222,7 @@
       <c r="M69" s="82"/>
       <c r="N69" s="82"/>
       <c r="Q69" s="3" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
     </row>
     <row r="70" spans="1:21" customHeight="1" ht="13.8">
@@ -11769,7 +12241,7 @@
       <c r="M70" s="82"/>
       <c r="N70" s="82"/>
       <c r="Q70" s="3" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" spans="1:21" customHeight="1" ht="13.8">
@@ -11788,7 +12260,7 @@
       <c r="M71" s="82"/>
       <c r="N71" s="82"/>
       <c r="Q71" s="3" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
     </row>
     <row r="72" spans="1:21" customHeight="1" ht="13.8">
@@ -11807,7 +12279,7 @@
       <c r="M72" s="82"/>
       <c r="N72" s="82"/>
       <c r="Q72" s="3" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="73" spans="1:21" customHeight="1" ht="13.8">
@@ -11826,7 +12298,7 @@
       <c r="M73" s="82"/>
       <c r="N73" s="82"/>
       <c r="Q73" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:21" customHeight="1" ht="13.8">
@@ -11845,7 +12317,7 @@
       <c r="M74" s="82"/>
       <c r="N74" s="82"/>
       <c r="Q74" s="3" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:21" customHeight="1" ht="13.8">
@@ -11864,7 +12336,7 @@
       <c r="M75" s="82"/>
       <c r="N75" s="82"/>
       <c r="Q75" s="3" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
     </row>
     <row r="76" spans="1:21" customHeight="1" ht="13.8">
@@ -11883,7 +12355,7 @@
       <c r="M76" s="82"/>
       <c r="N76" s="82"/>
       <c r="Q76" s="3" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="1:21" customHeight="1" ht="13.8">
@@ -11902,7 +12374,7 @@
       <c r="M77" s="82"/>
       <c r="N77" s="82"/>
       <c r="Q77" s="3" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
     </row>
     <row r="78" spans="1:21" customHeight="1" ht="13.8">
@@ -11921,7 +12393,7 @@
       <c r="M78" s="82"/>
       <c r="N78" s="82"/>
       <c r="Q78" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
     </row>
     <row r="79" spans="1:21" customHeight="1" ht="13.8">
@@ -11940,7 +12412,7 @@
       <c r="M79" s="82"/>
       <c r="N79" s="82"/>
       <c r="Q79" s="3" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
     </row>
     <row r="80" spans="1:21" customHeight="1" ht="13.8">
@@ -11959,7 +12431,7 @@
       <c r="M80" s="82"/>
       <c r="N80" s="82"/>
       <c r="Q80" s="3" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
     </row>
     <row r="81" spans="1:21" customHeight="1" ht="13.8">
@@ -11978,7 +12450,7 @@
       <c r="M81" s="82"/>
       <c r="N81" s="82"/>
       <c r="Q81" s="3" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
     </row>
     <row r="82" spans="1:21" customHeight="1" ht="13.8">
@@ -11997,7 +12469,7 @@
       <c r="M82" s="82"/>
       <c r="N82" s="82"/>
       <c r="Q82" s="3" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
     </row>
     <row r="83" spans="1:21" customHeight="1" ht="13.8">
@@ -12016,7 +12488,7 @@
       <c r="M83" s="82"/>
       <c r="N83" s="82"/>
       <c r="Q83" s="3" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" spans="1:21" customHeight="1" ht="13.8">
@@ -12035,7 +12507,7 @@
       <c r="M84" s="82"/>
       <c r="N84" s="82"/>
       <c r="Q84" s="3" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
     </row>
     <row r="85" spans="1:21" customHeight="1" ht="27.6">
@@ -12054,7 +12526,7 @@
       <c r="M85" s="82"/>
       <c r="N85" s="82"/>
       <c r="Q85" s="3" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:21" customHeight="1" ht="13.8">
@@ -12073,7 +12545,7 @@
       <c r="M86" s="82"/>
       <c r="N86" s="82"/>
       <c r="Q86" s="3" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
     </row>
     <row r="87" spans="1:21" customHeight="1" ht="13.8">
@@ -12092,7 +12564,7 @@
       <c r="M87" s="82"/>
       <c r="N87" s="82"/>
       <c r="Q87" s="3" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
     </row>
     <row r="88" spans="1:21" customHeight="1" ht="13.8">
@@ -12111,7 +12583,7 @@
       <c r="M88" s="82"/>
       <c r="N88" s="82"/>
       <c r="Q88" s="3" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89" spans="1:21" customHeight="1" ht="13.8">
@@ -12130,7 +12602,7 @@
       <c r="M89" s="82"/>
       <c r="N89" s="82"/>
       <c r="Q89" s="3" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="1:21" customHeight="1" ht="13.8">
@@ -12149,7 +12621,7 @@
       <c r="M90" s="82"/>
       <c r="N90" s="82"/>
       <c r="Q90" s="3" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
     </row>
     <row r="91" spans="1:21" customHeight="1" ht="13.8">
@@ -12168,7 +12640,7 @@
       <c r="M91" s="82"/>
       <c r="N91" s="82"/>
       <c r="Q91" s="3" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
     </row>
     <row r="92" spans="1:21" customHeight="1" ht="13.8">
@@ -12187,7 +12659,7 @@
       <c r="M92" s="82"/>
       <c r="N92" s="82"/>
       <c r="Q92" s="3" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
     </row>
     <row r="93" spans="1:21" customHeight="1" ht="13.8">
@@ -12195,7 +12667,7 @@
       <c r="B93" s="82"/>
       <c r="C93" s="82"/>
       <c r="D93" s="217" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="E93" s="82"/>
       <c r="F93" s="82"/>
@@ -12208,7 +12680,7 @@
       <c r="M93" s="82"/>
       <c r="N93" s="82"/>
       <c r="Q93" s="3" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
     </row>
     <row r="94" spans="1:21" customHeight="1" ht="13.8">
@@ -12227,7 +12699,7 @@
       <c r="M94" s="82"/>
       <c r="N94" s="82"/>
       <c r="Q94" s="3" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
     </row>
     <row r="95" spans="1:21" customHeight="1" ht="13.8">
@@ -12246,7 +12718,7 @@
       <c r="M95" s="82"/>
       <c r="N95" s="82"/>
       <c r="Q95" s="3" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" spans="1:21" customHeight="1" ht="13.8">
@@ -12265,7 +12737,7 @@
       <c r="M96" s="82"/>
       <c r="N96" s="82"/>
       <c r="Q96" s="3" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
     </row>
     <row r="97" spans="1:21" customHeight="1" ht="13.8">
@@ -12284,7 +12756,7 @@
       <c r="M97" s="82"/>
       <c r="N97" s="82"/>
       <c r="Q97" s="3" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
     </row>
     <row r="98" spans="1:21" customHeight="1" ht="13.8">
@@ -12303,7 +12775,7 @@
       <c r="M98" s="82"/>
       <c r="N98" s="82"/>
       <c r="Q98" s="3" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:21" customHeight="1" ht="13.8">
@@ -12322,7 +12794,7 @@
       <c r="M99" s="82"/>
       <c r="N99" s="82"/>
       <c r="Q99" s="3" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
     </row>
     <row r="100" spans="1:21" customHeight="1" ht="13.8">
@@ -12341,7 +12813,7 @@
       <c r="M100" s="82"/>
       <c r="N100" s="82"/>
       <c r="Q100" s="3" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
     </row>
     <row r="101" spans="1:21" customHeight="1" ht="13.8">
@@ -12360,7 +12832,7 @@
       <c r="M101" s="82"/>
       <c r="N101" s="82"/>
       <c r="Q101" s="3" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
     </row>
     <row r="102" spans="1:21" customHeight="1" ht="13.8">
@@ -12379,7 +12851,7 @@
       <c r="M102" s="82"/>
       <c r="N102" s="82"/>
       <c r="Q102" s="3" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
     </row>
     <row r="103" spans="1:21" customHeight="1" ht="13.8">
@@ -12398,7 +12870,7 @@
       <c r="M103" s="82"/>
       <c r="N103" s="82"/>
       <c r="Q103" s="3" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
     </row>
     <row r="104" spans="1:21" customHeight="1" ht="13.8">
@@ -12417,7 +12889,7 @@
       <c r="M104" s="82"/>
       <c r="N104" s="82"/>
       <c r="Q104" s="3" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105" spans="1:21" customHeight="1" ht="13.8">
@@ -12436,7 +12908,7 @@
       <c r="M105" s="82"/>
       <c r="N105" s="82"/>
       <c r="Q105" s="3" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" spans="1:21" customHeight="1" ht="13.8">
@@ -12455,7 +12927,7 @@
       <c r="M106" s="82"/>
       <c r="N106" s="82"/>
       <c r="Q106" s="3" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
     </row>
     <row r="107" spans="1:21" customHeight="1" ht="13.8">
@@ -12474,7 +12946,7 @@
       <c r="M107" s="82"/>
       <c r="N107" s="82"/>
       <c r="Q107" s="3" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
     </row>
     <row r="108" spans="1:21" customHeight="1" ht="13.8">
@@ -12493,7 +12965,7 @@
       <c r="M108" s="82"/>
       <c r="N108" s="82"/>
       <c r="Q108" s="3" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
     </row>
     <row r="109" spans="1:21" customHeight="1" ht="13.8">
@@ -12512,7 +12984,7 @@
       <c r="M109" s="82"/>
       <c r="N109" s="82"/>
       <c r="Q109" s="3" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
     </row>
     <row r="110" spans="1:21" customHeight="1" ht="13.8">
@@ -12531,7 +13003,7 @@
       <c r="M110" s="82"/>
       <c r="N110" s="82"/>
       <c r="Q110" s="3" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
     </row>
     <row r="111" spans="1:21" customHeight="1" ht="13.8">
@@ -12550,7 +13022,7 @@
       <c r="M111" s="82"/>
       <c r="N111" s="82"/>
       <c r="Q111" s="3" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
     </row>
     <row r="112" spans="1:21" customHeight="1" ht="13.8">
@@ -12569,7 +13041,7 @@
       <c r="M112" s="82"/>
       <c r="N112" s="82"/>
       <c r="Q112" s="3" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
     </row>
     <row r="113" spans="1:21" customHeight="1" ht="13.8">
@@ -12588,7 +13060,7 @@
       <c r="M113" s="82"/>
       <c r="N113" s="82"/>
       <c r="Q113" s="3" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
     </row>
     <row r="114" spans="1:21" customHeight="1" ht="13.8">
@@ -12607,7 +13079,7 @@
       <c r="M114" s="82"/>
       <c r="N114" s="82"/>
       <c r="Q114" s="3" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
     </row>
     <row r="115" spans="1:21" customHeight="1" ht="13.8">
@@ -12626,7 +13098,7 @@
       <c r="M115" s="82"/>
       <c r="N115" s="82"/>
       <c r="Q115" s="3" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:21" customHeight="1" ht="13.8">
@@ -12645,7 +13117,7 @@
       <c r="M116" s="82"/>
       <c r="N116" s="82"/>
       <c r="Q116" s="3" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
     </row>
     <row r="117" spans="1:21" customHeight="1" ht="13.8">
@@ -12664,7 +13136,7 @@
       <c r="M117" s="82"/>
       <c r="N117" s="82"/>
       <c r="Q117" s="3" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
     </row>
     <row r="118" spans="1:21" customHeight="1" ht="13.8">
@@ -12683,7 +13155,7 @@
       <c r="M118" s="82"/>
       <c r="N118" s="82"/>
       <c r="Q118" s="3" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
     </row>
     <row r="119" spans="1:21" customHeight="1" ht="13.8">
@@ -12702,7 +13174,7 @@
       <c r="M119" s="82"/>
       <c r="N119" s="82"/>
       <c r="Q119" s="3" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
     </row>
     <row r="120" spans="1:21" customHeight="1" ht="13.8">
@@ -12721,7 +13193,7 @@
       <c r="M120" s="82"/>
       <c r="N120" s="82"/>
       <c r="Q120" s="3" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
     </row>
     <row r="121" spans="1:21" customHeight="1" ht="13.8">
@@ -12740,7 +13212,7 @@
       <c r="M121" s="82"/>
       <c r="N121" s="82"/>
       <c r="Q121" s="3" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
     </row>
     <row r="122" spans="1:21" customHeight="1" ht="13.8">
@@ -12759,7 +13231,7 @@
       <c r="M122" s="82"/>
       <c r="N122" s="82"/>
       <c r="Q122" s="3" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
     </row>
     <row r="123" spans="1:21" customHeight="1" ht="13.8">
@@ -12778,7 +13250,7 @@
       <c r="M123" s="82"/>
       <c r="N123" s="82"/>
       <c r="Q123" s="3" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
     </row>
     <row r="124" spans="1:21" customHeight="1" ht="13.8">
@@ -12797,7 +13269,7 @@
       <c r="M124" s="82"/>
       <c r="N124" s="82"/>
       <c r="Q124" s="3" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
     </row>
     <row r="125" spans="1:21" customHeight="1" ht="13.8">
@@ -12816,7 +13288,7 @@
       <c r="M125" s="82"/>
       <c r="N125" s="82"/>
       <c r="Q125" s="3" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
     </row>
     <row r="126" spans="1:21" customHeight="1" ht="13.8">
@@ -12835,7 +13307,7 @@
       <c r="M126" s="82"/>
       <c r="N126" s="82"/>
       <c r="Q126" s="3" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
     </row>
     <row r="127" spans="1:21" customHeight="1" ht="13.8">
@@ -12854,7 +13326,7 @@
       <c r="M127" s="82"/>
       <c r="N127" s="82"/>
       <c r="Q127" s="3" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
     </row>
     <row r="128" spans="1:21" customHeight="1" ht="27.6">
@@ -12873,7 +13345,7 @@
       <c r="M128" s="82"/>
       <c r="N128" s="82"/>
       <c r="Q128" s="3" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
     </row>
     <row r="129" spans="1:21" customHeight="1" ht="13.8">
@@ -12892,7 +13364,7 @@
       <c r="M129" s="82"/>
       <c r="N129" s="82"/>
       <c r="Q129" s="3" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
     </row>
     <row r="130" spans="1:21" customHeight="1" ht="13.8">
@@ -12911,7 +13383,7 @@
       <c r="M130" s="82"/>
       <c r="N130" s="82"/>
       <c r="Q130" s="3" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
     </row>
     <row r="131" spans="1:21" customHeight="1" ht="13.8">
@@ -12930,7 +13402,7 @@
       <c r="M131" s="82"/>
       <c r="N131" s="82"/>
       <c r="Q131" s="3" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row r="132" spans="1:21" customHeight="1" ht="13.8">
@@ -12949,7 +13421,7 @@
       <c r="M132" s="82"/>
       <c r="N132" s="82"/>
       <c r="Q132" s="3" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
     </row>
     <row r="133" spans="1:21" customHeight="1" ht="13.8">
@@ -12968,7 +13440,7 @@
       <c r="M133" s="82"/>
       <c r="N133" s="82"/>
       <c r="Q133" s="3" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
     </row>
     <row r="134" spans="1:21" customHeight="1" ht="13.8">
@@ -12987,7 +13459,7 @@
       <c r="M134" s="82"/>
       <c r="N134" s="82"/>
       <c r="Q134" s="3" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
     </row>
     <row r="135" spans="1:21" customHeight="1" ht="13.8">
@@ -13006,7 +13478,7 @@
       <c r="M135" s="82"/>
       <c r="N135" s="82"/>
       <c r="Q135" s="3" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
     </row>
     <row r="136" spans="1:21" customHeight="1" ht="13.8">
@@ -13025,7 +13497,7 @@
       <c r="M136" s="82"/>
       <c r="N136" s="82"/>
       <c r="Q136" s="3" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
     </row>
     <row r="137" spans="1:21" customHeight="1" ht="13.8">
@@ -13044,7 +13516,7 @@
       <c r="M137" s="82"/>
       <c r="N137" s="82"/>
       <c r="Q137" s="3" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
     </row>
     <row r="138" spans="1:21" customHeight="1" ht="13.8">
@@ -13063,7 +13535,7 @@
       <c r="M138" s="82"/>
       <c r="N138" s="82"/>
       <c r="Q138" s="3" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
     </row>
     <row r="139" spans="1:21" customHeight="1" ht="13.8">
@@ -13082,7 +13554,7 @@
       <c r="M139" s="82"/>
       <c r="N139" s="82"/>
       <c r="Q139" s="3" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
     </row>
     <row r="140" spans="1:21" customHeight="1" ht="13.8">
@@ -13101,7 +13573,7 @@
       <c r="M140" s="82"/>
       <c r="N140" s="82"/>
       <c r="Q140" s="3" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
     </row>
     <row r="141" spans="1:21" customHeight="1" ht="13.8">
@@ -13120,7 +13592,7 @@
       <c r="M141" s="82"/>
       <c r="N141" s="82"/>
       <c r="Q141" s="3" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
     </row>
     <row r="142" spans="1:21" customHeight="1" ht="13.8">
@@ -13139,7 +13611,7 @@
       <c r="M142" s="82"/>
       <c r="N142" s="82"/>
       <c r="Q142" s="3" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
     </row>
     <row r="143" spans="1:21" customHeight="1" ht="27.6">
@@ -13158,7 +13630,7 @@
       <c r="M143" s="82"/>
       <c r="N143" s="82"/>
       <c r="Q143" s="3" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:21" customHeight="1" ht="13.8">
@@ -13177,7 +13649,7 @@
       <c r="M144" s="82"/>
       <c r="N144" s="82"/>
       <c r="Q144" s="3" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
     </row>
     <row r="145" spans="1:21" customHeight="1" ht="13.8">
@@ -13196,7 +13668,7 @@
       <c r="M145" s="82"/>
       <c r="N145" s="82"/>
       <c r="Q145" s="3" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
     </row>
     <row r="146" spans="1:21" customHeight="1" ht="13.8">
@@ -13215,7 +13687,7 @@
       <c r="M146" s="82"/>
       <c r="N146" s="82"/>
       <c r="Q146" s="3" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
     </row>
     <row r="147" spans="1:21" customHeight="1" ht="13.8">
@@ -13234,7 +13706,7 @@
       <c r="M147" s="82"/>
       <c r="N147" s="82"/>
       <c r="Q147" s="3" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
     </row>
     <row r="148" spans="1:21" customHeight="1" ht="13.8">
@@ -13253,7 +13725,7 @@
       <c r="M148" s="82"/>
       <c r="N148" s="82"/>
       <c r="Q148" s="3" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
     </row>
     <row r="149" spans="1:21" customHeight="1" ht="13.8">
@@ -13272,7 +13744,7 @@
       <c r="M149" s="82"/>
       <c r="N149" s="82"/>
       <c r="Q149" s="3" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
     </row>
     <row r="150" spans="1:21" customHeight="1" ht="13.8">
@@ -13291,7 +13763,7 @@
       <c r="M150" s="82"/>
       <c r="N150" s="82"/>
       <c r="Q150" s="3" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
     </row>
     <row r="151" spans="1:21" customHeight="1" ht="13.8">
@@ -13310,7 +13782,7 @@
       <c r="M151" s="82"/>
       <c r="N151" s="82"/>
       <c r="Q151" s="3" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row r="152" spans="1:21" customHeight="1" ht="13.8">
@@ -13329,7 +13801,7 @@
       <c r="M152" s="82"/>
       <c r="N152" s="82"/>
       <c r="Q152" s="3" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
     </row>
     <row r="153" spans="1:21" customHeight="1" ht="27.6">
@@ -13348,7 +13820,7 @@
       <c r="M153" s="82"/>
       <c r="N153" s="82"/>
       <c r="Q153" s="3" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
     </row>
     <row r="154" spans="1:21" customHeight="1" ht="13.8">
@@ -13367,7 +13839,7 @@
       <c r="M154" s="82"/>
       <c r="N154" s="82"/>
       <c r="Q154" s="3" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
     </row>
     <row r="155" spans="1:21" customHeight="1" ht="27.6">
@@ -13386,7 +13858,7 @@
       <c r="M155" s="82"/>
       <c r="N155" s="82"/>
       <c r="Q155" s="3" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
     </row>
     <row r="156" spans="1:21" customHeight="1" ht="13.8">
@@ -13405,7 +13877,7 @@
       <c r="M156" s="82"/>
       <c r="N156" s="82"/>
       <c r="Q156" s="3" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="157" spans="1:21" customHeight="1" ht="13.8">
@@ -13424,7 +13896,7 @@
       <c r="M157" s="82"/>
       <c r="N157" s="82"/>
       <c r="Q157" s="3" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
     </row>
     <row r="158" spans="1:21" customHeight="1" ht="13.8">
@@ -13443,7 +13915,7 @@
       <c r="M158" s="82"/>
       <c r="N158" s="82"/>
       <c r="Q158" s="3" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
     </row>
     <row r="159" spans="1:21" customHeight="1" ht="13.8">
@@ -13462,7 +13934,7 @@
       <c r="M159" s="82"/>
       <c r="N159" s="82"/>
       <c r="Q159" s="3" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
     </row>
     <row r="160" spans="1:21" customHeight="1" ht="13.8">
@@ -13481,7 +13953,7 @@
       <c r="M160" s="82"/>
       <c r="N160" s="82"/>
       <c r="Q160" s="3" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
     </row>
     <row r="161" spans="1:21" customHeight="1" ht="13.8">
@@ -13500,7 +13972,7 @@
       <c r="M161" s="82"/>
       <c r="N161" s="82"/>
       <c r="Q161" s="3" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
     </row>
     <row r="162" spans="1:21" customHeight="1" ht="13.8">
@@ -13519,7 +13991,7 @@
       <c r="M162" s="82"/>
       <c r="N162" s="82"/>
       <c r="Q162" s="3" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
     </row>
     <row r="163" spans="1:21" customHeight="1" ht="13.8">
@@ -13538,7 +14010,7 @@
       <c r="M163" s="82"/>
       <c r="N163" s="82"/>
       <c r="Q163" s="3" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
     </row>
     <row r="164" spans="1:21" customHeight="1" ht="13.8">
@@ -13557,7 +14029,7 @@
       <c r="M164" s="82"/>
       <c r="N164" s="82"/>
       <c r="Q164" s="3" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
     </row>
     <row r="165" spans="1:21" customHeight="1" ht="27.6">
@@ -13576,7 +14048,7 @@
       <c r="M165" s="82"/>
       <c r="N165" s="82"/>
       <c r="Q165" s="3" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
     </row>
     <row r="166" spans="1:21" customHeight="1" ht="13.8">
@@ -13595,7 +14067,7 @@
       <c r="M166" s="82"/>
       <c r="N166" s="82"/>
       <c r="Q166" s="3" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:21" customHeight="1" ht="41.4">
@@ -13614,7 +14086,7 @@
       <c r="M167" s="82"/>
       <c r="N167" s="82"/>
       <c r="Q167" s="3" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
     </row>
     <row r="168" spans="1:21" customHeight="1" ht="13.8">
@@ -13633,7 +14105,7 @@
       <c r="M168" s="82"/>
       <c r="N168" s="82"/>
       <c r="Q168" s="3" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
     </row>
     <row r="169" spans="1:21" customHeight="1" ht="13.8">
@@ -13652,7 +14124,7 @@
       <c r="M169" s="82"/>
       <c r="N169" s="82"/>
       <c r="Q169" s="3" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
     </row>
     <row r="170" spans="1:21" customHeight="1" ht="27.6">
@@ -13671,7 +14143,7 @@
       <c r="M170" s="82"/>
       <c r="N170" s="82"/>
       <c r="Q170" s="3" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
     </row>
     <row r="171" spans="1:21" customHeight="1" ht="13.8">
@@ -13690,7 +14162,7 @@
       <c r="M171" s="82"/>
       <c r="N171" s="82"/>
       <c r="Q171" s="3" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
     </row>
     <row r="172" spans="1:21" customHeight="1" ht="13.8">
@@ -13709,7 +14181,7 @@
       <c r="M172" s="82"/>
       <c r="N172" s="82"/>
       <c r="Q172" s="3" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
     </row>
     <row r="173" spans="1:21" customHeight="1" ht="13.8">
@@ -13728,7 +14200,7 @@
       <c r="M173" s="82"/>
       <c r="N173" s="82"/>
       <c r="Q173" s="3" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
     </row>
     <row r="174" spans="1:21" customHeight="1" ht="13.8">
@@ -13747,7 +14219,7 @@
       <c r="M174" s="82"/>
       <c r="N174" s="82"/>
       <c r="Q174" s="3" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
     </row>
     <row r="175" spans="1:21" customHeight="1" ht="13.8">
@@ -13766,7 +14238,7 @@
       <c r="M175" s="82"/>
       <c r="N175" s="82"/>
       <c r="Q175" s="3" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
     </row>
     <row r="176" spans="1:21" customHeight="1" ht="13.8">
@@ -13785,7 +14257,7 @@
       <c r="M176" s="82"/>
       <c r="N176" s="82"/>
       <c r="Q176" s="3" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
     </row>
     <row r="177" spans="1:21" customHeight="1" ht="13.8">
@@ -13804,7 +14276,7 @@
       <c r="M177" s="82"/>
       <c r="N177" s="82"/>
       <c r="Q177" s="3" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
     </row>
     <row r="178" spans="1:21" customHeight="1" ht="13.8">
@@ -13823,7 +14295,7 @@
       <c r="M178" s="82"/>
       <c r="N178" s="82"/>
       <c r="Q178" s="3" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
     </row>
     <row r="179" spans="1:21" customHeight="1" ht="13.8">
@@ -13842,7 +14314,7 @@
       <c r="M179" s="82"/>
       <c r="N179" s="82"/>
       <c r="Q179" s="3" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
     </row>
     <row r="180" spans="1:21" customHeight="1" ht="27.6">
@@ -13861,7 +14333,7 @@
       <c r="M180" s="82"/>
       <c r="N180" s="82"/>
       <c r="Q180" s="3" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
     </row>
     <row r="181" spans="1:21" customHeight="1" ht="13.8">
@@ -13880,7 +14352,7 @@
       <c r="M181" s="82"/>
       <c r="N181" s="82"/>
       <c r="Q181" s="3" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
     </row>
     <row r="182" spans="1:21" customHeight="1" ht="13.8">
@@ -13899,7 +14371,7 @@
       <c r="M182" s="82"/>
       <c r="N182" s="82"/>
       <c r="Q182" s="3" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
     </row>
     <row r="183" spans="1:21" customHeight="1" ht="13.8">
@@ -13918,7 +14390,7 @@
       <c r="M183" s="82"/>
       <c r="N183" s="82"/>
       <c r="Q183" s="3" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
     </row>
     <row r="184" spans="1:21" customHeight="1" ht="13.8">
@@ -13937,7 +14409,7 @@
       <c r="M184" s="82"/>
       <c r="N184" s="82"/>
       <c r="Q184" s="3" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
     </row>
     <row r="185" spans="1:21" customHeight="1" ht="13.8">
@@ -13956,7 +14428,7 @@
       <c r="M185" s="82"/>
       <c r="N185" s="82"/>
       <c r="Q185" s="3" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
     </row>
     <row r="186" spans="1:21" customHeight="1" ht="13.8">
@@ -13975,7 +14447,7 @@
       <c r="M186" s="82"/>
       <c r="N186" s="82"/>
       <c r="Q186" s="3" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
     </row>
     <row r="187" spans="1:21" customHeight="1" ht="13.8">
@@ -13994,7 +14466,7 @@
       <c r="M187" s="82"/>
       <c r="N187" s="82"/>
       <c r="Q187" s="3" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
     </row>
     <row r="188" spans="1:21" customHeight="1" ht="13.8">
@@ -14013,7 +14485,7 @@
       <c r="M188" s="82"/>
       <c r="N188" s="82"/>
       <c r="Q188" s="3" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
     </row>
     <row r="189" spans="1:21" customHeight="1" ht="13.8">
@@ -14032,7 +14504,7 @@
       <c r="M189" s="82"/>
       <c r="N189" s="82"/>
       <c r="Q189" s="3" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
     </row>
     <row r="190" spans="1:21" customHeight="1" ht="13.8">
@@ -14051,7 +14523,7 @@
       <c r="M190" s="82"/>
       <c r="N190" s="82"/>
       <c r="Q190" s="3" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
     </row>
     <row r="191" spans="1:21" customHeight="1" ht="13.8">
@@ -14070,7 +14542,7 @@
       <c r="M191" s="82"/>
       <c r="N191" s="82"/>
       <c r="Q191" s="3" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
     </row>
     <row r="192" spans="1:21" customHeight="1" ht="13.8">
@@ -14089,7 +14561,7 @@
       <c r="M192" s="82"/>
       <c r="N192" s="82"/>
       <c r="Q192" s="3" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
     </row>
     <row r="193" spans="1:21" customHeight="1" ht="13.8">
@@ -14108,7 +14580,7 @@
       <c r="M193" s="82"/>
       <c r="N193" s="82"/>
       <c r="Q193" s="3" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
     </row>
     <row r="194" spans="1:21" customHeight="1" ht="13.8">
@@ -14127,7 +14599,7 @@
       <c r="M194" s="82"/>
       <c r="N194" s="82"/>
       <c r="Q194" s="3" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
     </row>
     <row r="195" spans="1:21" customHeight="1" ht="13.8">
@@ -14146,7 +14618,7 @@
       <c r="M195" s="82"/>
       <c r="N195" s="82"/>
       <c r="Q195" s="3" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
     </row>
     <row r="196" spans="1:21" customHeight="1" ht="13.8">
@@ -14165,7 +14637,7 @@
       <c r="M196" s="82"/>
       <c r="N196" s="82"/>
       <c r="Q196" s="3" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
     </row>
     <row r="197" spans="1:21" customHeight="1" ht="13.8">
@@ -14184,7 +14656,7 @@
       <c r="M197" s="82"/>
       <c r="N197" s="82"/>
       <c r="Q197" s="3" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
     </row>
     <row r="198" spans="1:21" customHeight="1" ht="13.8">
@@ -14203,7 +14675,7 @@
       <c r="M198" s="82"/>
       <c r="N198" s="82"/>
       <c r="Q198" s="3" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
     </row>
     <row r="199" spans="1:21" customHeight="1" ht="13.8">
@@ -14222,7 +14694,7 @@
       <c r="M199" s="82"/>
       <c r="N199" s="82"/>
       <c r="Q199" s="3" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:21" customHeight="1" ht="27.6">
@@ -14241,7 +14713,7 @@
       <c r="M200" s="82"/>
       <c r="N200" s="82"/>
       <c r="Q200" s="3" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
     </row>
     <row r="201" spans="1:21" customHeight="1" ht="13.8">
@@ -14260,7 +14732,7 @@
       <c r="M201" s="82"/>
       <c r="N201" s="82"/>
       <c r="Q201" s="3" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row r="202" spans="1:21" customHeight="1" ht="13.8">
@@ -14279,7 +14751,7 @@
       <c r="M202" s="82"/>
       <c r="N202" s="82"/>
       <c r="Q202" s="3" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
     </row>
     <row r="203" spans="1:21" customHeight="1" ht="13.8">
@@ -14298,7 +14770,7 @@
       <c r="M203" s="82"/>
       <c r="N203" s="82"/>
       <c r="Q203" s="3" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
     </row>
     <row r="204" spans="1:21" customHeight="1" ht="13.8">
@@ -14317,7 +14789,7 @@
       <c r="M204" s="82"/>
       <c r="N204" s="82"/>
       <c r="Q204" s="3" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
     </row>
     <row r="205" spans="1:21" customHeight="1" ht="13.8">
@@ -14336,7 +14808,7 @@
       <c r="M205" s="82"/>
       <c r="N205" s="82"/>
       <c r="Q205" s="3" t="s">
-        <v>304</v>
+        <v>334</v>
       </c>
     </row>
     <row r="206" spans="1:21" customHeight="1" ht="13.8">
@@ -14355,7 +14827,7 @@
       <c r="M206" s="82"/>
       <c r="N206" s="82"/>
       <c r="Q206" s="3" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
     </row>
     <row r="207" spans="1:21" customHeight="1" ht="27.6">
@@ -14374,7 +14846,7 @@
       <c r="M207" s="82"/>
       <c r="N207" s="82"/>
       <c r="Q207" s="3" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
     </row>
     <row r="208" spans="1:21" customHeight="1" ht="27.6">
@@ -14393,7 +14865,7 @@
       <c r="M208" s="82"/>
       <c r="N208" s="82"/>
       <c r="Q208" s="3" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
     </row>
     <row r="209" spans="1:21" customHeight="1" ht="13.8">
@@ -14412,7 +14884,7 @@
       <c r="M209" s="82"/>
       <c r="N209" s="82"/>
       <c r="Q209" s="3" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
     </row>
     <row r="210" spans="1:21" customHeight="1" ht="13.8">
@@ -14431,7 +14903,7 @@
       <c r="M210" s="82"/>
       <c r="N210" s="82"/>
       <c r="Q210" s="3" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
     </row>
     <row r="211" spans="1:21" customHeight="1" ht="13.8">
@@ -14450,7 +14922,7 @@
       <c r="M211" s="82"/>
       <c r="N211" s="82"/>
       <c r="Q211" s="3" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
     </row>
     <row r="212" spans="1:21" customHeight="1" ht="13.8">
@@ -14469,7 +14941,7 @@
       <c r="M212" s="82"/>
       <c r="N212" s="82"/>
       <c r="Q212" s="3" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
     </row>
     <row r="213" spans="1:21" customHeight="1" ht="13.8">
@@ -14488,7 +14960,7 @@
       <c r="M213" s="82"/>
       <c r="N213" s="82"/>
       <c r="Q213" s="3" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
     </row>
     <row r="214" spans="1:21" customHeight="1" ht="13.8">
@@ -14507,7 +14979,7 @@
       <c r="M214" s="82"/>
       <c r="N214" s="82"/>
       <c r="Q214" s="3" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
     </row>
     <row r="215" spans="1:21" customHeight="1" ht="13.8">
@@ -14526,7 +14998,7 @@
       <c r="M215" s="82"/>
       <c r="N215" s="82"/>
       <c r="Q215" s="3" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
     </row>
     <row r="216" spans="1:21" customHeight="1" ht="13.8">
@@ -14545,7 +15017,7 @@
       <c r="M216" s="82"/>
       <c r="N216" s="82"/>
       <c r="Q216" s="3" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
     </row>
     <row r="217" spans="1:21">
@@ -15970,7 +16442,7 @@
     </row>
     <row r="2" spans="1:12" customHeight="1" ht="18">
       <c r="A2" s="474" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="B2" s="475"/>
       <c r="C2" s="475"/>
@@ -15985,26 +16457,26 @@
     </row>
     <row r="3" spans="1:12" customHeight="1" ht="15">
       <c r="A3" s="114" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="B3" s="466" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="C3" s="466"/>
       <c r="D3" s="466"/>
       <c r="E3" s="467"/>
       <c r="F3" s="472" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="G3" s="468" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="H3" s="467"/>
       <c r="I3" s="468" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="J3" s="470" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="K3" s="471"/>
     </row>
@@ -16019,24 +16491,36 @@
       <c r="H4" s="456"/>
       <c r="I4" s="469"/>
       <c r="J4" s="5" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="K4" s="221" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:12" customHeight="1" ht="27">
-      <c r="A5" s="711"/>
+      <c r="A5" s="711" t="s">
+        <v>355</v>
+      </c>
       <c r="B5" s="712"/>
       <c r="C5" s="712"/>
       <c r="D5" s="712"/>
       <c r="E5" s="712"/>
-      <c r="F5" s="691"/>
-      <c r="G5" s="713"/>
+      <c r="F5" s="691">
+        <v>81.17</v>
+      </c>
+      <c r="G5" s="713" t="s">
+        <v>356</v>
+      </c>
       <c r="H5" s="713"/>
-      <c r="I5" s="691"/>
-      <c r="J5" s="691"/>
-      <c r="K5" s="714"/>
+      <c r="I5" s="691" t="s">
+        <v>357</v>
+      </c>
+      <c r="J5" s="691">
+        <v>135329</v>
+      </c>
+      <c r="K5" s="714" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="6" spans="1:12" customHeight="1" ht="27">
       <c r="A6" s="711"/>
@@ -16118,7 +16602,7 @@
     </row>
     <row r="12" spans="1:12" customHeight="1" ht="12">
       <c r="A12" s="457" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B12" s="458"/>
       <c r="C12" s="458"/>
@@ -16133,7 +16617,7 @@
     </row>
     <row r="13" spans="1:12" customHeight="1" ht="18">
       <c r="A13" s="460" t="s">
-        <v>325</v>
+        <v>359</v>
       </c>
       <c r="B13" s="461"/>
       <c r="C13" s="461"/>
@@ -16148,7 +16632,7 @@
     </row>
     <row r="14" spans="1:12" customHeight="1" ht="12">
       <c r="A14" s="171" t="s">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="B14" s="74"/>
       <c r="C14" s="74"/>
@@ -16163,27 +16647,27 @@
     </row>
     <row r="15" spans="1:12" customHeight="1" ht="18">
       <c r="A15" s="4" t="s">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="B15" s="453" t="s">
-        <v>328</v>
+        <v>362</v>
       </c>
       <c r="C15" s="454"/>
       <c r="D15" s="481" t="s">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="E15" s="453"/>
       <c r="F15" s="454"/>
       <c r="G15" s="481" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="H15" s="453"/>
       <c r="I15" s="454"/>
       <c r="J15" s="442" t="s">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="K15" s="477" t="s">
-        <v>332</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:12" customHeight="1" ht="15">
@@ -16201,11 +16685,11 @@
     </row>
     <row r="17" spans="1:12" customHeight="1" ht="18.75">
       <c r="A17" s="479" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="B17" s="480"/>
       <c r="C17" s="7" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="D17" s="469"/>
       <c r="E17" s="455"/>
@@ -16217,82 +16701,154 @@
       <c r="K17" s="478"/>
     </row>
     <row r="18" spans="1:12" customHeight="1" ht="24" s="8" customFormat="1">
-      <c r="A18" s="699"/>
+      <c r="A18" s="699" t="s">
+        <v>367</v>
+      </c>
       <c r="B18" s="700"/>
-      <c r="C18" s="701"/>
-      <c r="D18" s="702"/>
+      <c r="C18" s="701" t="s">
+        <v>368</v>
+      </c>
+      <c r="D18" s="702" t="s">
+        <v>369</v>
+      </c>
       <c r="E18" s="702"/>
       <c r="F18" s="702"/>
-      <c r="G18" s="702"/>
+      <c r="G18" s="702" t="s">
+        <v>370</v>
+      </c>
       <c r="H18" s="702"/>
       <c r="I18" s="702"/>
-      <c r="J18" s="703"/>
-      <c r="K18" s="704"/>
+      <c r="J18" s="703" t="s">
+        <v>371</v>
+      </c>
+      <c r="K18" s="704" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="19" spans="1:12" customHeight="1" ht="24" s="8" customFormat="1">
-      <c r="A19" s="699"/>
+      <c r="A19" s="699" t="s">
+        <v>373</v>
+      </c>
       <c r="B19" s="700"/>
-      <c r="C19" s="701"/>
-      <c r="D19" s="702"/>
+      <c r="C19" s="701" t="s">
+        <v>374</v>
+      </c>
+      <c r="D19" s="702" t="s">
+        <v>375</v>
+      </c>
       <c r="E19" s="702"/>
       <c r="F19" s="702"/>
-      <c r="G19" s="702"/>
+      <c r="G19" s="702" t="s">
+        <v>376</v>
+      </c>
       <c r="H19" s="702"/>
       <c r="I19" s="702"/>
-      <c r="J19" s="703"/>
-      <c r="K19" s="704"/>
+      <c r="J19" s="703" t="s">
+        <v>377</v>
+      </c>
+      <c r="K19" s="704" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="20" spans="1:12" customHeight="1" ht="24" s="8" customFormat="1">
-      <c r="A20" s="699"/>
+      <c r="A20" s="699" t="s">
+        <v>379</v>
+      </c>
       <c r="B20" s="700"/>
-      <c r="C20" s="701"/>
-      <c r="D20" s="702"/>
+      <c r="C20" s="701" t="s">
+        <v>380</v>
+      </c>
+      <c r="D20" s="702" t="s">
+        <v>369</v>
+      </c>
       <c r="E20" s="702"/>
       <c r="F20" s="702"/>
-      <c r="G20" s="702"/>
+      <c r="G20" s="702" t="s">
+        <v>381</v>
+      </c>
       <c r="H20" s="702"/>
       <c r="I20" s="702"/>
-      <c r="J20" s="703"/>
-      <c r="K20" s="704"/>
+      <c r="J20" s="703" t="s">
+        <v>377</v>
+      </c>
+      <c r="K20" s="704" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="21" spans="1:12" customHeight="1" ht="24" s="8" customFormat="1">
-      <c r="A21" s="699"/>
+      <c r="A21" s="699" t="s">
+        <v>382</v>
+      </c>
       <c r="B21" s="700"/>
-      <c r="C21" s="701"/>
-      <c r="D21" s="702"/>
+      <c r="C21" s="701" t="s">
+        <v>383</v>
+      </c>
+      <c r="D21" s="702" t="s">
+        <v>384</v>
+      </c>
       <c r="E21" s="702"/>
       <c r="F21" s="702"/>
-      <c r="G21" s="702"/>
+      <c r="G21" s="702" t="s">
+        <v>381</v>
+      </c>
       <c r="H21" s="702"/>
       <c r="I21" s="702"/>
-      <c r="J21" s="703"/>
-      <c r="K21" s="704"/>
+      <c r="J21" s="703" t="s">
+        <v>377</v>
+      </c>
+      <c r="K21" s="704" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="22" spans="1:12" customHeight="1" ht="24" s="8" customFormat="1">
-      <c r="A22" s="699"/>
+      <c r="A22" s="699" t="s">
+        <v>385</v>
+      </c>
       <c r="B22" s="700"/>
-      <c r="C22" s="701"/>
-      <c r="D22" s="702"/>
+      <c r="C22" s="701" t="s">
+        <v>386</v>
+      </c>
+      <c r="D22" s="702" t="s">
+        <v>387</v>
+      </c>
       <c r="E22" s="702"/>
       <c r="F22" s="702"/>
-      <c r="G22" s="702"/>
+      <c r="G22" s="702" t="s">
+        <v>381</v>
+      </c>
       <c r="H22" s="702"/>
       <c r="I22" s="702"/>
-      <c r="J22" s="703"/>
-      <c r="K22" s="704"/>
+      <c r="J22" s="703" t="s">
+        <v>377</v>
+      </c>
+      <c r="K22" s="704" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="23" spans="1:12" customHeight="1" ht="24" s="8" customFormat="1">
-      <c r="A23" s="699"/>
+      <c r="A23" s="699" t="s">
+        <v>388</v>
+      </c>
       <c r="B23" s="700"/>
-      <c r="C23" s="701"/>
-      <c r="D23" s="702"/>
+      <c r="C23" s="701" t="s">
+        <v>389</v>
+      </c>
+      <c r="D23" s="702" t="s">
+        <v>390</v>
+      </c>
       <c r="E23" s="702"/>
       <c r="F23" s="702"/>
-      <c r="G23" s="702"/>
+      <c r="G23" s="702" t="s">
+        <v>391</v>
+      </c>
       <c r="H23" s="702"/>
       <c r="I23" s="702"/>
-      <c r="J23" s="703"/>
-      <c r="K23" s="704"/>
+      <c r="J23" s="703" t="s">
+        <v>377</v>
+      </c>
+      <c r="K23" s="704" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="24" spans="1:12" customHeight="1" ht="24" s="8" customFormat="1">
       <c r="A24" s="699"/>
@@ -16582,7 +17138,7 @@
     </row>
     <row r="46" spans="1:12" customHeight="1" ht="9.75">
       <c r="A46" s="444" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B46" s="445"/>
       <c r="C46" s="445"/>
@@ -16597,30 +17153,30 @@
     </row>
     <row r="47" spans="1:12" customHeight="1" ht="27.75">
       <c r="A47" s="420" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="B47" s="421"/>
       <c r="C47" s="422"/>
       <c r="D47" s="450" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E47" s="451"/>
       <c r="F47" s="451"/>
       <c r="G47" s="451"/>
       <c r="H47" s="452"/>
       <c r="I47" s="200" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="J47" s="448">
         <f>NOW()</f>
-        <v>46200.595543981</v>
+        <v>46302.639039352</v>
       </c>
       <c r="K47" s="449"/>
       <c r="L47" s="201"/>
     </row>
     <row r="48" spans="1:12" customHeight="1" ht="9">
       <c r="A48" s="419" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="B48" s="419"/>
       <c r="C48" s="419"/>
@@ -16637,7 +17193,7 @@
     <row r="60" spans="1:12">
       <c r="L60" s="237">
         <f>NOW()</f>
-        <v>46200.595543981</v>
+        <v>46302.639039352</v>
       </c>
     </row>
   </sheetData>
@@ -16815,7 +17371,7 @@
     </row>
     <row r="2" spans="1:13" customHeight="1" ht="22.5">
       <c r="A2" s="518" t="s">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="B2" s="519"/>
       <c r="C2" s="519"/>
@@ -16830,22 +17386,22 @@
     </row>
     <row r="3" spans="1:13" customHeight="1" ht="15">
       <c r="A3" s="502" t="s">
-        <v>335</v>
+        <v>394</v>
       </c>
       <c r="B3" s="503" t="s">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="C3" s="503"/>
       <c r="D3" s="504"/>
       <c r="E3" s="466" t="s">
-        <v>337</v>
+        <v>396</v>
       </c>
       <c r="F3" s="467"/>
       <c r="G3" s="530" t="s">
-        <v>338</v>
+        <v>397</v>
       </c>
       <c r="H3" s="468" t="s">
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="I3" s="513"/>
       <c r="J3" s="513"/>
@@ -16870,10 +17426,10 @@
       <c r="C5" s="521"/>
       <c r="D5" s="522"/>
       <c r="E5" s="10" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="G5" s="532"/>
       <c r="H5" s="517"/>
@@ -16974,7 +17530,7 @@
     </row>
     <row r="13" spans="1:13" customHeight="1" ht="11.25">
       <c r="A13" s="457" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B13" s="458"/>
       <c r="C13" s="458"/>
@@ -16989,7 +17545,7 @@
     </row>
     <row r="14" spans="1:13" customHeight="1" ht="18">
       <c r="A14" s="485" t="s">
-        <v>340</v>
+        <v>399</v>
       </c>
       <c r="B14" s="486"/>
       <c r="C14" s="486"/>
@@ -17004,25 +17560,25 @@
     </row>
     <row r="15" spans="1:13" customHeight="1" ht="18">
       <c r="A15" s="490" t="s">
-        <v>341</v>
+        <v>400</v>
       </c>
       <c r="B15" s="453" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
       <c r="C15" s="494"/>
       <c r="D15" s="495"/>
       <c r="E15" s="453" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
       <c r="F15" s="454"/>
       <c r="G15" s="488" t="s">
-        <v>338</v>
+        <v>397</v>
       </c>
       <c r="H15" s="500" t="s">
-        <v>344</v>
+        <v>403</v>
       </c>
       <c r="I15" s="481" t="s">
-        <v>345</v>
+        <v>404</v>
       </c>
       <c r="J15" s="494"/>
       <c r="K15" s="516"/>
@@ -17046,10 +17602,10 @@
       <c r="C17" s="386"/>
       <c r="D17" s="496"/>
       <c r="E17" s="10" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="G17" s="489"/>
       <c r="H17" s="501"/>
@@ -17058,171 +17614,327 @@
       <c r="K17" s="387"/>
     </row>
     <row r="18" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A18" s="722"/>
+      <c r="A18" s="722" t="s">
+        <v>405</v>
+      </c>
       <c r="B18" s="723"/>
       <c r="C18" s="723"/>
       <c r="D18" s="716"/>
-      <c r="E18" s="724"/>
-      <c r="F18" s="724"/>
-      <c r="G18" s="724"/>
-      <c r="H18" s="724"/>
-      <c r="I18" s="715"/>
+      <c r="E18" s="724" t="s">
+        <v>406</v>
+      </c>
+      <c r="F18" s="724" t="s">
+        <v>406</v>
+      </c>
+      <c r="G18" s="724">
+        <v>21</v>
+      </c>
+      <c r="H18" s="724" t="s">
+        <v>407</v>
+      </c>
+      <c r="I18" s="715" t="s">
+        <v>408</v>
+      </c>
       <c r="J18" s="725"/>
       <c r="K18" s="726"/>
     </row>
     <row r="19" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A19" s="722"/>
+      <c r="A19" s="722" t="s">
+        <v>409</v>
+      </c>
       <c r="B19" s="723"/>
       <c r="C19" s="723"/>
       <c r="D19" s="716"/>
-      <c r="E19" s="724"/>
-      <c r="F19" s="724"/>
-      <c r="G19" s="724"/>
-      <c r="H19" s="724"/>
-      <c r="I19" s="727"/>
+      <c r="E19" s="724" t="s">
+        <v>410</v>
+      </c>
+      <c r="F19" s="724" t="s">
+        <v>410</v>
+      </c>
+      <c r="G19" s="724">
+        <v>8</v>
+      </c>
+      <c r="H19" s="724" t="s">
+        <v>407</v>
+      </c>
+      <c r="I19" s="727" t="s">
+        <v>411</v>
+      </c>
       <c r="J19" s="728"/>
       <c r="K19" s="729"/>
     </row>
     <row r="20" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A20" s="722"/>
+      <c r="A20" s="722" t="s">
+        <v>412</v>
+      </c>
       <c r="B20" s="723"/>
       <c r="C20" s="723"/>
       <c r="D20" s="716"/>
-      <c r="E20" s="724"/>
-      <c r="F20" s="724"/>
-      <c r="G20" s="724"/>
-      <c r="H20" s="724"/>
-      <c r="I20" s="727"/>
+      <c r="E20" s="724" t="s">
+        <v>413</v>
+      </c>
+      <c r="F20" s="724" t="s">
+        <v>413</v>
+      </c>
+      <c r="G20" s="724">
+        <v>8</v>
+      </c>
+      <c r="H20" s="724" t="s">
+        <v>407</v>
+      </c>
+      <c r="I20" s="727" t="s">
+        <v>411</v>
+      </c>
       <c r="J20" s="728"/>
       <c r="K20" s="729"/>
     </row>
     <row r="21" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A21" s="722"/>
+      <c r="A21" s="722" t="s">
+        <v>414</v>
+      </c>
       <c r="B21" s="723"/>
       <c r="C21" s="723"/>
       <c r="D21" s="716"/>
-      <c r="E21" s="724"/>
-      <c r="F21" s="724"/>
-      <c r="G21" s="724"/>
-      <c r="H21" s="724"/>
-      <c r="I21" s="727"/>
+      <c r="E21" s="724" t="s">
+        <v>415</v>
+      </c>
+      <c r="F21" s="724" t="s">
+        <v>415</v>
+      </c>
+      <c r="G21" s="724">
+        <v>6</v>
+      </c>
+      <c r="H21" s="724" t="s">
+        <v>407</v>
+      </c>
+      <c r="I21" s="727" t="s">
+        <v>411</v>
+      </c>
       <c r="J21" s="728"/>
       <c r="K21" s="729"/>
     </row>
     <row r="22" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A22" s="722"/>
+      <c r="A22" s="722" t="s">
+        <v>416</v>
+      </c>
       <c r="B22" s="723"/>
       <c r="C22" s="723"/>
       <c r="D22" s="716"/>
-      <c r="E22" s="724"/>
-      <c r="F22" s="724"/>
-      <c r="G22" s="724"/>
-      <c r="H22" s="724"/>
-      <c r="I22" s="727"/>
+      <c r="E22" s="724" t="s">
+        <v>417</v>
+      </c>
+      <c r="F22" s="724" t="s">
+        <v>417</v>
+      </c>
+      <c r="G22" s="724">
+        <v>8</v>
+      </c>
+      <c r="H22" s="724" t="s">
+        <v>407</v>
+      </c>
+      <c r="I22" s="727" t="s">
+        <v>411</v>
+      </c>
       <c r="J22" s="728"/>
       <c r="K22" s="729"/>
     </row>
     <row r="23" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A23" s="722"/>
+      <c r="A23" s="722" t="s">
+        <v>418</v>
+      </c>
       <c r="B23" s="723"/>
       <c r="C23" s="723"/>
       <c r="D23" s="716"/>
-      <c r="E23" s="724"/>
-      <c r="F23" s="724"/>
-      <c r="G23" s="724"/>
-      <c r="H23" s="724"/>
-      <c r="I23" s="727"/>
+      <c r="E23" s="724" t="s">
+        <v>419</v>
+      </c>
+      <c r="F23" s="724" t="s">
+        <v>419</v>
+      </c>
+      <c r="G23" s="724">
+        <v>24</v>
+      </c>
+      <c r="H23" s="724" t="s">
+        <v>420</v>
+      </c>
+      <c r="I23" s="727" t="s">
+        <v>421</v>
+      </c>
       <c r="J23" s="728"/>
       <c r="K23" s="729"/>
     </row>
     <row r="24" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A24" s="722"/>
+      <c r="A24" s="722" t="s">
+        <v>422</v>
+      </c>
       <c r="B24" s="723"/>
       <c r="C24" s="723"/>
       <c r="D24" s="716"/>
-      <c r="E24" s="724"/>
-      <c r="F24" s="724"/>
-      <c r="G24" s="724"/>
-      <c r="H24" s="724"/>
-      <c r="I24" s="727"/>
+      <c r="E24" s="724" t="s">
+        <v>423</v>
+      </c>
+      <c r="F24" s="724" t="s">
+        <v>424</v>
+      </c>
+      <c r="G24" s="724">
+        <v>18</v>
+      </c>
+      <c r="H24" s="724" t="s">
+        <v>407</v>
+      </c>
+      <c r="I24" s="727" t="s">
+        <v>408</v>
+      </c>
       <c r="J24" s="728"/>
       <c r="K24" s="729"/>
     </row>
     <row r="25" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A25" s="722"/>
+      <c r="A25" s="722" t="s">
+        <v>425</v>
+      </c>
       <c r="B25" s="723"/>
       <c r="C25" s="723"/>
       <c r="D25" s="716"/>
-      <c r="E25" s="724"/>
-      <c r="F25" s="724"/>
-      <c r="G25" s="724"/>
-      <c r="H25" s="724"/>
-      <c r="I25" s="727"/>
+      <c r="E25" s="724" t="s">
+        <v>426</v>
+      </c>
+      <c r="F25" s="724" t="s">
+        <v>426</v>
+      </c>
+      <c r="G25" s="724">
+        <v>12</v>
+      </c>
+      <c r="H25" s="724" t="s">
+        <v>407</v>
+      </c>
+      <c r="I25" s="727" t="s">
+        <v>408</v>
+      </c>
       <c r="J25" s="728"/>
       <c r="K25" s="729"/>
     </row>
     <row r="26" spans="1:13" customHeight="1" ht="24">
-      <c r="A26" s="722"/>
+      <c r="A26" s="722" t="s">
+        <v>427</v>
+      </c>
       <c r="B26" s="723"/>
       <c r="C26" s="723"/>
       <c r="D26" s="716"/>
-      <c r="E26" s="724"/>
-      <c r="F26" s="724"/>
-      <c r="G26" s="724"/>
-      <c r="H26" s="724"/>
-      <c r="I26" s="715"/>
+      <c r="E26" s="724" t="s">
+        <v>428</v>
+      </c>
+      <c r="F26" s="724" t="s">
+        <v>429</v>
+      </c>
+      <c r="G26" s="724">
+        <v>24</v>
+      </c>
+      <c r="H26" s="724" t="s">
+        <v>407</v>
+      </c>
+      <c r="I26" s="715" t="s">
+        <v>430</v>
+      </c>
       <c r="J26" s="725"/>
       <c r="K26" s="726"/>
     </row>
     <row r="27" spans="1:13" customHeight="1" ht="24">
-      <c r="A27" s="722"/>
+      <c r="A27" s="722" t="s">
+        <v>431</v>
+      </c>
       <c r="B27" s="723"/>
       <c r="C27" s="723"/>
       <c r="D27" s="716"/>
-      <c r="E27" s="724"/>
-      <c r="F27" s="724"/>
-      <c r="G27" s="724"/>
-      <c r="H27" s="724"/>
-      <c r="I27" s="715"/>
+      <c r="E27" s="724" t="s">
+        <v>432</v>
+      </c>
+      <c r="F27" s="724" t="s">
+        <v>432</v>
+      </c>
+      <c r="G27" s="724">
+        <v>1</v>
+      </c>
+      <c r="H27" s="724" t="s">
+        <v>407</v>
+      </c>
+      <c r="I27" s="715" t="s">
+        <v>411</v>
+      </c>
       <c r="J27" s="725"/>
       <c r="K27" s="726"/>
     </row>
     <row r="28" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A28" s="722"/>
+      <c r="A28" s="722" t="s">
+        <v>433</v>
+      </c>
       <c r="B28" s="723"/>
       <c r="C28" s="723"/>
       <c r="D28" s="716"/>
-      <c r="E28" s="724"/>
-      <c r="F28" s="724"/>
-      <c r="G28" s="724"/>
-      <c r="H28" s="724"/>
-      <c r="I28" s="715"/>
+      <c r="E28" s="724" t="s">
+        <v>434</v>
+      </c>
+      <c r="F28" s="724" t="s">
+        <v>435</v>
+      </c>
+      <c r="G28" s="724">
+        <v>1</v>
+      </c>
+      <c r="H28" s="724" t="s">
+        <v>407</v>
+      </c>
+      <c r="I28" s="715" t="s">
+        <v>411</v>
+      </c>
       <c r="J28" s="725"/>
       <c r="K28" s="726"/>
     </row>
     <row r="29" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A29" s="730"/>
+      <c r="A29" s="730" t="s">
+        <v>436</v>
+      </c>
       <c r="B29" s="731"/>
       <c r="C29" s="731"/>
       <c r="D29" s="685"/>
-      <c r="E29" s="724"/>
-      <c r="F29" s="724"/>
-      <c r="G29" s="724"/>
-      <c r="H29" s="724"/>
-      <c r="I29" s="727"/>
+      <c r="E29" s="724" t="s">
+        <v>437</v>
+      </c>
+      <c r="F29" s="724" t="s">
+        <v>437</v>
+      </c>
+      <c r="G29" s="724">
+        <v>4</v>
+      </c>
+      <c r="H29" s="724" t="s">
+        <v>407</v>
+      </c>
+      <c r="I29" s="727" t="s">
+        <v>411</v>
+      </c>
       <c r="J29" s="728"/>
       <c r="K29" s="729"/>
     </row>
     <row r="30" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A30" s="730"/>
+      <c r="A30" s="730" t="s">
+        <v>438</v>
+      </c>
       <c r="B30" s="731"/>
       <c r="C30" s="731"/>
       <c r="D30" s="685"/>
-      <c r="E30" s="724"/>
-      <c r="F30" s="724"/>
-      <c r="G30" s="724"/>
-      <c r="H30" s="724"/>
-      <c r="I30" s="727"/>
+      <c r="E30" s="724" t="s">
+        <v>439</v>
+      </c>
+      <c r="F30" s="724" t="s">
+        <v>440</v>
+      </c>
+      <c r="G30" s="724">
+        <v>40</v>
+      </c>
+      <c r="H30" s="724" t="s">
+        <v>407</v>
+      </c>
+      <c r="I30" s="727" t="s">
+        <v>407</v>
+      </c>
       <c r="J30" s="728"/>
       <c r="K30" s="729"/>
     </row>
@@ -17332,7 +18044,7 @@
     </row>
     <row r="39" spans="1:13" customHeight="1" ht="13.8">
       <c r="A39" s="423" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B39" s="424"/>
       <c r="C39" s="424"/>
@@ -17347,7 +18059,7 @@
     </row>
     <row r="40" spans="1:13" customHeight="1" ht="22.5">
       <c r="A40" s="527" t="s">
-        <v>346</v>
+        <v>441</v>
       </c>
       <c r="B40" s="528"/>
       <c r="C40" s="528"/>
@@ -17362,46 +18074,56 @@
     </row>
     <row r="41" spans="1:13" customHeight="1" ht="33.75">
       <c r="A41" s="115" t="s">
-        <v>347</v>
+        <v>442</v>
       </c>
       <c r="B41" s="122" t="s">
-        <v>348</v>
+        <v>443</v>
       </c>
       <c r="C41" s="116" t="s">
-        <v>349</v>
+        <v>444</v>
       </c>
       <c r="D41" s="533" t="s">
-        <v>350</v>
+        <v>445</v>
       </c>
       <c r="E41" s="533"/>
       <c r="F41" s="533"/>
       <c r="G41" s="533"/>
       <c r="H41" s="534"/>
       <c r="I41" s="116" t="s">
-        <v>351</v>
+        <v>446</v>
       </c>
       <c r="J41" s="533" t="s">
-        <v>352</v>
+        <v>447</v>
       </c>
       <c r="K41" s="270"/>
     </row>
     <row r="42" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A42" s="523"/>
+      <c r="A42" s="523" t="s">
+        <v>448</v>
+      </c>
       <c r="B42" s="524"/>
-      <c r="C42" s="525"/>
+      <c r="C42" s="525" t="s">
+        <v>449</v>
+      </c>
       <c r="D42" s="526"/>
       <c r="E42" s="526"/>
       <c r="F42" s="526"/>
       <c r="G42" s="526"/>
       <c r="H42" s="524"/>
-      <c r="I42" s="525"/>
+      <c r="I42" s="525" t="s">
+        <v>57</v>
+      </c>
       <c r="J42" s="526"/>
       <c r="K42" s="535"/>
     </row>
     <row r="43" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A43" s="523"/>
+      <c r="A43" s="523" t="s">
+        <v>450</v>
+      </c>
       <c r="B43" s="524"/>
-      <c r="C43" s="525"/>
+      <c r="C43" s="525" t="s">
+        <v>451</v>
+      </c>
       <c r="D43" s="526"/>
       <c r="E43" s="526"/>
       <c r="F43" s="526"/>
@@ -17412,9 +18134,13 @@
       <c r="K43" s="535"/>
     </row>
     <row r="44" spans="1:13" customHeight="1" ht="24.75">
-      <c r="A44" s="523"/>
+      <c r="A44" s="523" t="s">
+        <v>452</v>
+      </c>
       <c r="B44" s="524"/>
-      <c r="C44" s="525"/>
+      <c r="C44" s="525" t="s">
+        <v>453</v>
+      </c>
       <c r="D44" s="526"/>
       <c r="E44" s="526"/>
       <c r="F44" s="526"/>
@@ -17427,7 +18153,9 @@
     <row r="45" spans="1:13" customHeight="1" ht="24.75">
       <c r="A45" s="523"/>
       <c r="B45" s="524"/>
-      <c r="C45" s="525"/>
+      <c r="C45" s="525" t="s">
+        <v>454</v>
+      </c>
       <c r="D45" s="526"/>
       <c r="E45" s="526"/>
       <c r="F45" s="526"/>
@@ -17478,7 +18206,7 @@
     </row>
     <row r="49" spans="1:13" customHeight="1" ht="11.25">
       <c r="A49" s="423" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B49" s="424"/>
       <c r="C49" s="424"/>
@@ -17493,22 +18221,22 @@
     </row>
     <row r="50" spans="1:13" customHeight="1" ht="28.5">
       <c r="A50" s="420" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="B50" s="422"/>
       <c r="C50" s="450" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="D50" s="538"/>
       <c r="E50" s="538"/>
       <c r="F50" s="539"/>
       <c r="G50" s="536" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="H50" s="537"/>
       <c r="I50" s="740">
         <f>NOW()</f>
-        <v>46200.595543981</v>
+        <v>46302.639039352</v>
       </c>
       <c r="J50" s="741"/>
       <c r="K50" s="742"/>
@@ -17517,7 +18245,7 @@
     </row>
     <row r="51" spans="1:13" customHeight="1" ht="9.75">
       <c r="K51" s="205" t="s">
-        <v>353</v>
+        <v>455</v>
       </c>
     </row>
     <row r="52" spans="1:13" customHeight="1" ht="3"/>
@@ -17672,11 +18400,11 @@
     </row>
     <row r="2" spans="1:23" customHeight="1" ht="13.5">
       <c r="A2" s="595" t="s">
-        <v>354</v>
+        <v>456</v>
       </c>
       <c r="B2" s="596"/>
       <c r="C2" s="577" t="s">
-        <v>355</v>
+        <v>457</v>
       </c>
       <c r="D2" s="577"/>
       <c r="E2" s="577"/>
@@ -17702,7 +18430,7 @@
       <c r="A3" s="17"/>
       <c r="B3" s="18"/>
       <c r="C3" s="580" t="s">
-        <v>356</v>
+        <v>458</v>
       </c>
       <c r="D3" s="580"/>
       <c r="E3" s="580"/>
@@ -17728,7 +18456,7 @@
       <c r="A4" s="17"/>
       <c r="B4" s="18"/>
       <c r="C4" s="580" t="s">
-        <v>357</v>
+        <v>459</v>
       </c>
       <c r="D4" s="580"/>
       <c r="E4" s="580"/>
@@ -17738,10 +18466,10 @@
       <c r="P4" s="231"/>
       <c r="Q4" s="231"/>
       <c r="R4" s="231" t="s">
-        <v>358</v>
+        <v>460</v>
       </c>
       <c r="S4" s="231" t="s">
-        <v>359</v>
+        <v>461</v>
       </c>
       <c r="T4" s="231"/>
       <c r="U4" s="231"/>
@@ -17776,7 +18504,7 @@
       <c r="A6" s="17"/>
       <c r="B6" s="18"/>
       <c r="C6" s="580" t="s">
-        <v>360</v>
+        <v>462</v>
       </c>
       <c r="D6" s="580"/>
       <c r="E6" s="580"/>
@@ -17791,17 +18519,23 @@
         <v>34</v>
       </c>
       <c r="Q6" s="231" t="s">
-        <v>361</v>
-      </c>
-      <c r="R6" s="232"/>
-      <c r="S6" s="232"/>
+        <v>463</v>
+      </c>
+      <c r="R6" s="232" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" s="232" t="b">
+        <v>1</v>
+      </c>
       <c r="T6" s="232" t="s">
-        <v>362</v>
+        <v>464</v>
       </c>
       <c r="U6" s="232" t="b">
         <v>0</v>
       </c>
-      <c r="V6" s="232"/>
+      <c r="V6" s="232" t="b">
+        <v>1</v>
+      </c>
       <c r="W6" s="234"/>
     </row>
     <row r="7" spans="1:23" customHeight="1" ht="3">
@@ -17830,7 +18564,7 @@
       <c r="A8" s="17"/>
       <c r="B8" s="18"/>
       <c r="C8" s="580" t="s">
-        <v>363</v>
+        <v>465</v>
       </c>
       <c r="D8" s="580"/>
       <c r="E8" s="580"/>
@@ -17841,10 +18575,14 @@
         <v>35</v>
       </c>
       <c r="Q8" s="231" t="s">
-        <v>361</v>
-      </c>
-      <c r="R8" s="232"/>
-      <c r="S8" s="232"/>
+        <v>463</v>
+      </c>
+      <c r="R8" s="232" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" s="232" t="b">
+        <v>1</v>
+      </c>
       <c r="T8" s="232"/>
       <c r="U8" s="232"/>
       <c r="V8" s="232"/>
@@ -17876,7 +18614,7 @@
       <c r="E10" s="580"/>
       <c r="F10" s="581"/>
       <c r="G10" s="562" t="s">
-        <v>364</v>
+        <v>466</v>
       </c>
       <c r="H10" s="562"/>
       <c r="I10" s="562"/>
@@ -17887,13 +18625,13 @@
       <c r="O10" s="234"/>
       <c r="P10" s="231"/>
       <c r="Q10" s="231" t="s">
-        <v>362</v>
+        <v>464</v>
       </c>
       <c r="R10" s="232" t="b">
         <v>0</v>
       </c>
       <c r="S10" s="232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="232"/>
       <c r="U10" s="232"/>
@@ -17919,8 +18657,12 @@
         <v>36</v>
       </c>
       <c r="Q11" s="231"/>
-      <c r="R11" s="232"/>
-      <c r="S11" s="232"/>
+      <c r="R11" s="232" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" s="232" t="b">
+        <v>1</v>
+      </c>
       <c r="T11" s="232"/>
       <c r="U11" s="232"/>
       <c r="V11" s="232"/>
@@ -17952,11 +18694,11 @@
     </row>
     <row r="13" spans="1:23" customHeight="1" ht="18">
       <c r="A13" s="558" t="s">
-        <v>365</v>
+        <v>467</v>
       </c>
       <c r="B13" s="559"/>
       <c r="C13" s="560" t="s">
-        <v>366</v>
+        <v>468</v>
       </c>
       <c r="D13" s="560"/>
       <c r="E13" s="494"/>
@@ -17973,8 +18715,12 @@
         <v>37</v>
       </c>
       <c r="Q13" s="231"/>
-      <c r="R13" s="232"/>
-      <c r="S13" s="232"/>
+      <c r="R13" s="232" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13" s="232" t="b">
+        <v>1</v>
+      </c>
       <c r="T13" s="232"/>
       <c r="U13" s="232"/>
       <c r="V13" s="232"/>
@@ -17988,7 +18734,7 @@
       <c r="E14" s="494"/>
       <c r="F14" s="495"/>
       <c r="G14" s="561" t="s">
-        <v>364</v>
+        <v>466</v>
       </c>
       <c r="H14" s="562"/>
       <c r="I14" s="562"/>
@@ -18001,10 +18747,14 @@
         <v>38</v>
       </c>
       <c r="Q14" s="231" t="s">
-        <v>361</v>
-      </c>
-      <c r="R14" s="232"/>
-      <c r="S14" s="232"/>
+        <v>463</v>
+      </c>
+      <c r="R14" s="232" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" s="232" t="b">
+        <v>1</v>
+      </c>
       <c r="T14" s="232"/>
       <c r="U14" s="232"/>
       <c r="V14" s="232"/>
@@ -18027,10 +18777,14 @@
       <c r="O15" s="234"/>
       <c r="P15" s="231"/>
       <c r="Q15" s="231" t="s">
-        <v>362</v>
-      </c>
-      <c r="R15" s="232"/>
-      <c r="S15" s="232"/>
+        <v>464</v>
+      </c>
+      <c r="R15" s="232" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15" s="232" t="b">
+        <v>1</v>
+      </c>
       <c r="T15" s="232"/>
       <c r="U15" s="232"/>
       <c r="V15" s="232"/>
@@ -18088,7 +18842,7 @@
       <c r="A18" s="29"/>
       <c r="B18" s="30"/>
       <c r="C18" s="677" t="s">
-        <v>367</v>
+        <v>469</v>
       </c>
       <c r="D18" s="677"/>
       <c r="E18" s="678"/>
@@ -18105,8 +18859,12 @@
         <v>39</v>
       </c>
       <c r="Q18" s="231"/>
-      <c r="R18" s="232"/>
-      <c r="S18" s="232"/>
+      <c r="R18" s="232" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" s="232" t="b">
+        <v>1</v>
+      </c>
       <c r="T18" s="232"/>
       <c r="U18" s="232"/>
       <c r="V18" s="232"/>
@@ -18120,7 +18878,7 @@
       <c r="E19" s="678"/>
       <c r="F19" s="679"/>
       <c r="G19" s="561" t="s">
-        <v>364</v>
+        <v>466</v>
       </c>
       <c r="H19" s="562"/>
       <c r="I19" s="562"/>
@@ -18133,10 +18891,14 @@
         <v>40</v>
       </c>
       <c r="Q19" s="231" t="s">
-        <v>361</v>
-      </c>
-      <c r="R19" s="232"/>
-      <c r="S19" s="232"/>
+        <v>463</v>
+      </c>
+      <c r="R19" s="232" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" s="232" t="b">
+        <v>1</v>
+      </c>
       <c r="T19" s="232"/>
       <c r="U19" s="232"/>
       <c r="V19" s="232"/>
@@ -18151,7 +18913,7 @@
       <c r="F20" s="679"/>
       <c r="G20" s="34"/>
       <c r="H20" s="551" t="s">
-        <v>368</v>
+        <v>470</v>
       </c>
       <c r="I20" s="551"/>
       <c r="J20" s="216"/>
@@ -18161,10 +18923,14 @@
       <c r="O20" s="234"/>
       <c r="P20" s="231"/>
       <c r="Q20" s="231" t="s">
-        <v>362</v>
-      </c>
-      <c r="R20" s="232"/>
-      <c r="S20" s="232"/>
+        <v>464</v>
+      </c>
+      <c r="R20" s="232" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" s="232" t="b">
+        <v>1</v>
+      </c>
       <c r="T20" s="232"/>
       <c r="U20" s="232"/>
       <c r="V20" s="232"/>
@@ -18178,7 +18944,7 @@
       <c r="E21" s="678"/>
       <c r="F21" s="679"/>
       <c r="G21" s="552" t="s">
-        <v>369</v>
+        <v>471</v>
       </c>
       <c r="H21" s="553"/>
       <c r="I21" s="553"/>
@@ -18189,10 +18955,14 @@
       <c r="O21" s="234"/>
       <c r="P21" s="231"/>
       <c r="Q21" s="231" t="s">
-        <v>370</v>
-      </c>
-      <c r="R21" s="232"/>
-      <c r="S21" s="232"/>
+        <v>472</v>
+      </c>
+      <c r="R21" s="232" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21" s="232" t="b">
+        <v>1</v>
+      </c>
       <c r="T21" s="232"/>
       <c r="U21" s="232"/>
       <c r="V21" s="232"/>
@@ -18206,7 +18976,7 @@
       <c r="E22" s="680"/>
       <c r="F22" s="681"/>
       <c r="G22" s="99" t="s">
-        <v>371</v>
+        <v>473</v>
       </c>
       <c r="H22" s="206"/>
       <c r="I22" s="682"/>
@@ -18226,11 +18996,11 @@
     </row>
     <row r="23" spans="1:23" customHeight="1" ht="18">
       <c r="A23" s="554" t="s">
-        <v>372</v>
+        <v>474</v>
       </c>
       <c r="B23" s="555"/>
       <c r="C23" s="591" t="s">
-        <v>373</v>
+        <v>475</v>
       </c>
       <c r="D23" s="591"/>
       <c r="E23" s="591"/>
@@ -18260,7 +19030,7 @@
       <c r="E24" s="583"/>
       <c r="F24" s="582"/>
       <c r="G24" s="561" t="s">
-        <v>364</v>
+        <v>466</v>
       </c>
       <c r="H24" s="562"/>
       <c r="I24" s="562"/>
@@ -18328,11 +19098,11 @@
     </row>
     <row r="27" spans="1:23" customHeight="1" ht="14.25">
       <c r="A27" s="554" t="s">
-        <v>374</v>
+        <v>476</v>
       </c>
       <c r="B27" s="555"/>
       <c r="C27" s="591" t="s">
-        <v>375</v>
+        <v>477</v>
       </c>
       <c r="D27" s="591"/>
       <c r="E27" s="591"/>
@@ -18362,7 +19132,7 @@
       <c r="E28" s="583"/>
       <c r="F28" s="582"/>
       <c r="G28" s="561" t="s">
-        <v>364</v>
+        <v>466</v>
       </c>
       <c r="H28" s="562"/>
       <c r="I28" s="562"/>
@@ -18430,11 +19200,11 @@
     </row>
     <row r="31" spans="1:23" customHeight="1" ht="18">
       <c r="A31" s="554" t="s">
-        <v>376</v>
+        <v>478</v>
       </c>
       <c r="B31" s="555"/>
       <c r="C31" s="591" t="s">
-        <v>377</v>
+        <v>479</v>
       </c>
       <c r="D31" s="591"/>
       <c r="E31" s="591"/>
@@ -18464,7 +19234,7 @@
       <c r="E32" s="583"/>
       <c r="F32" s="582"/>
       <c r="G32" s="556" t="s">
-        <v>378</v>
+        <v>480</v>
       </c>
       <c r="H32" s="557"/>
       <c r="I32" s="557"/>
@@ -18501,7 +19271,7 @@
       <c r="A34" s="27"/>
       <c r="B34" s="28"/>
       <c r="C34" s="583" t="s">
-        <v>379</v>
+        <v>481</v>
       </c>
       <c r="D34" s="583"/>
       <c r="E34" s="583"/>
@@ -18522,7 +19292,7 @@
       <c r="E35" s="583"/>
       <c r="F35" s="582"/>
       <c r="G35" s="556" t="s">
-        <v>378</v>
+        <v>480</v>
       </c>
       <c r="H35" s="557"/>
       <c r="I35" s="557"/>
@@ -18547,11 +19317,11 @@
     </row>
     <row r="37" spans="1:23" customHeight="1" ht="18">
       <c r="A37" s="554" t="s">
-        <v>380</v>
+        <v>482</v>
       </c>
       <c r="B37" s="555"/>
       <c r="C37" s="586" t="s">
-        <v>381</v>
+        <v>483</v>
       </c>
       <c r="D37" s="586"/>
       <c r="E37" s="586"/>
@@ -18572,7 +19342,7 @@
       <c r="E38" s="560"/>
       <c r="F38" s="588"/>
       <c r="G38" s="561" t="s">
-        <v>382</v>
+        <v>484</v>
       </c>
       <c r="H38" s="562"/>
       <c r="I38" s="562"/>
@@ -18613,11 +19383,11 @@
     </row>
     <row r="41" spans="1:23" customHeight="1" ht="41.55">
       <c r="A41" s="584" t="s">
-        <v>383</v>
+        <v>485</v>
       </c>
       <c r="B41" s="585"/>
       <c r="C41" s="583" t="s">
-        <v>384</v>
+        <v>486</v>
       </c>
       <c r="D41" s="583"/>
       <c r="E41" s="583"/>
@@ -18647,11 +19417,11 @@
     </row>
     <row r="43" spans="1:23" customHeight="1" ht="13.5">
       <c r="A43" s="42" t="s">
-        <v>385</v>
+        <v>487</v>
       </c>
       <c r="B43" s="43"/>
       <c r="C43" s="583" t="s">
-        <v>386</v>
+        <v>488</v>
       </c>
       <c r="D43" s="583"/>
       <c r="E43" s="583"/>
@@ -18666,7 +19436,7 @@
       <c r="E44" s="583"/>
       <c r="F44" s="582"/>
       <c r="G44" s="161" t="s">
-        <v>387</v>
+        <v>489</v>
       </c>
       <c r="H44" s="209"/>
       <c r="I44" s="92"/>
@@ -18677,11 +19447,11 @@
     </row>
     <row r="45" spans="1:23" customHeight="1" ht="13.5">
       <c r="A45" s="42" t="s">
-        <v>388</v>
+        <v>490</v>
       </c>
       <c r="B45" s="43"/>
       <c r="C45" s="582" t="s">
-        <v>389</v>
+        <v>491</v>
       </c>
       <c r="D45" s="582"/>
       <c r="E45" s="582"/>
@@ -18696,7 +19466,7 @@
       <c r="E46" s="582"/>
       <c r="F46" s="582"/>
       <c r="G46" s="162" t="s">
-        <v>390</v>
+        <v>492</v>
       </c>
       <c r="H46" s="210"/>
       <c r="I46" s="92"/>
@@ -18708,11 +19478,11 @@
     </row>
     <row r="47" spans="1:23" customHeight="1" ht="13.5">
       <c r="A47" s="42" t="s">
-        <v>391</v>
+        <v>493</v>
       </c>
       <c r="B47" s="43"/>
       <c r="C47" s="583" t="s">
-        <v>392</v>
+        <v>494</v>
       </c>
       <c r="D47" s="583"/>
       <c r="E47" s="89"/>
@@ -18727,7 +19497,7 @@
       <c r="E48" s="608"/>
       <c r="F48" s="609"/>
       <c r="G48" s="163" t="s">
-        <v>390</v>
+        <v>492</v>
       </c>
       <c r="H48" s="211"/>
       <c r="I48" s="94"/>
@@ -18755,11 +19525,11 @@
     </row>
     <row r="50" spans="1:23" customHeight="1" ht="23.25">
       <c r="A50" s="674" t="s">
-        <v>393</v>
+        <v>495</v>
       </c>
       <c r="B50" s="675"/>
       <c r="C50" s="159" t="s">
-        <v>394</v>
+        <v>496</v>
       </c>
       <c r="D50" s="159"/>
       <c r="E50" s="159"/>
@@ -18774,17 +19544,17 @@
     </row>
     <row r="51" spans="1:23" customHeight="1" ht="18">
       <c r="A51" s="604" t="s">
-        <v>395</v>
+        <v>497</v>
       </c>
       <c r="B51" s="605"/>
       <c r="C51" s="605"/>
       <c r="D51" s="605"/>
       <c r="E51" s="606"/>
       <c r="F51" s="219" t="s">
-        <v>396</v>
+        <v>498</v>
       </c>
       <c r="G51" s="269" t="s">
-        <v>397</v>
+        <v>499</v>
       </c>
       <c r="H51" s="533"/>
       <c r="I51" s="270"/>
@@ -18794,13 +19564,19 @@
       <c r="M51" s="549"/>
     </row>
     <row r="52" spans="1:23" customHeight="1" ht="24">
-      <c r="A52" s="620"/>
+      <c r="A52" s="620" t="s">
+        <v>500</v>
+      </c>
       <c r="B52" s="621"/>
       <c r="C52" s="623"/>
       <c r="D52" s="623"/>
       <c r="E52" s="624"/>
-      <c r="F52" s="235"/>
-      <c r="G52" s="613"/>
+      <c r="F52" s="235" t="s">
+        <v>501</v>
+      </c>
+      <c r="G52" s="613" t="s">
+        <v>502</v>
+      </c>
       <c r="H52" s="614"/>
       <c r="I52" s="615"/>
       <c r="J52" s="547"/>
@@ -18809,13 +19585,19 @@
       <c r="M52" s="549"/>
     </row>
     <row r="53" spans="1:23" customHeight="1" ht="24">
-      <c r="A53" s="620"/>
+      <c r="A53" s="620" t="s">
+        <v>503</v>
+      </c>
       <c r="B53" s="621"/>
       <c r="C53" s="621"/>
       <c r="D53" s="621"/>
       <c r="E53" s="622"/>
-      <c r="F53" s="235"/>
-      <c r="G53" s="613"/>
+      <c r="F53" s="235" t="s">
+        <v>501</v>
+      </c>
+      <c r="G53" s="613" t="s">
+        <v>504</v>
+      </c>
       <c r="H53" s="614"/>
       <c r="I53" s="615"/>
       <c r="J53" s="547"/>
@@ -18824,13 +19606,19 @@
       <c r="M53" s="549"/>
     </row>
     <row r="54" spans="1:23" customHeight="1" ht="24">
-      <c r="A54" s="616"/>
+      <c r="A54" s="616" t="s">
+        <v>505</v>
+      </c>
       <c r="B54" s="617"/>
       <c r="C54" s="618"/>
       <c r="D54" s="618"/>
       <c r="E54" s="619"/>
-      <c r="F54" s="236"/>
-      <c r="G54" s="541"/>
+      <c r="F54" s="236" t="s">
+        <v>36</v>
+      </c>
+      <c r="G54" s="541" t="s">
+        <v>506</v>
+      </c>
       <c r="H54" s="542"/>
       <c r="I54" s="543"/>
       <c r="J54" s="547"/>
@@ -18840,11 +19628,11 @@
     </row>
     <row r="55" spans="1:23" customHeight="1" ht="39.75">
       <c r="A55" s="595" t="s">
-        <v>398</v>
+        <v>507</v>
       </c>
       <c r="B55" s="596"/>
       <c r="C55" s="625" t="s">
-        <v>399</v>
+        <v>508</v>
       </c>
       <c r="D55" s="625"/>
       <c r="E55" s="625"/>
@@ -18869,7 +19657,7 @@
       <c r="I56" s="213"/>
       <c r="J56" s="166"/>
       <c r="K56" s="550" t="s">
-        <v>400</v>
+        <v>509</v>
       </c>
       <c r="L56" s="550"/>
       <c r="M56" s="151"/>
@@ -18919,12 +19707,12 @@
     <row r="60" spans="1:23" customHeight="1" ht="32.55">
       <c r="A60" s="52"/>
       <c r="B60" s="667" t="s">
-        <v>401</v>
+        <v>510</v>
       </c>
       <c r="C60" s="668"/>
       <c r="D60" s="669"/>
       <c r="F60" s="658" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="G60" s="659"/>
       <c r="H60" s="659"/>
@@ -18936,10 +19724,12 @@
     <row r="61" spans="1:23" customHeight="1" ht="20.25">
       <c r="A61" s="52"/>
       <c r="B61" s="654" t="s">
-        <v>402</v>
+        <v>511</v>
       </c>
       <c r="C61" s="655"/>
-      <c r="D61" s="105"/>
+      <c r="D61" s="105" t="s">
+        <v>512</v>
+      </c>
       <c r="F61" s="661"/>
       <c r="G61" s="662"/>
       <c r="H61" s="662"/>
@@ -18951,10 +19741,12 @@
     <row r="62" spans="1:23" customHeight="1" ht="9">
       <c r="A62" s="52"/>
       <c r="B62" s="642" t="s">
-        <v>403</v>
+        <v>513</v>
       </c>
       <c r="C62" s="643"/>
-      <c r="D62" s="646"/>
+      <c r="D62" s="646" t="s">
+        <v>514</v>
+      </c>
       <c r="F62" s="664"/>
       <c r="G62" s="665"/>
       <c r="H62" s="665"/>
@@ -18969,7 +19761,7 @@
       <c r="C63" s="657"/>
       <c r="D63" s="670"/>
       <c r="F63" s="671" t="s">
-        <v>404</v>
+        <v>515</v>
       </c>
       <c r="G63" s="672"/>
       <c r="H63" s="672"/>
@@ -18981,13 +19773,15 @@
     <row r="64" spans="1:23" customHeight="1" ht="10.5">
       <c r="A64" s="52"/>
       <c r="B64" s="642" t="s">
-        <v>405</v>
+        <v>516</v>
       </c>
       <c r="C64" s="643"/>
-      <c r="D64" s="646"/>
+      <c r="D64" s="646" t="s">
+        <v>517</v>
+      </c>
       <c r="F64" s="743">
         <f> NOW()</f>
-        <v>46200.595543981</v>
+        <v>46302.639039352</v>
       </c>
       <c r="G64" s="744"/>
       <c r="H64" s="744"/>
@@ -19003,14 +19797,14 @@
       <c r="C65" s="645"/>
       <c r="D65" s="647"/>
       <c r="F65" s="639" t="s">
-        <v>406</v>
+        <v>518</v>
       </c>
       <c r="G65" s="640"/>
       <c r="H65" s="640"/>
       <c r="I65" s="641"/>
       <c r="J65" s="54"/>
       <c r="K65" s="637" t="s">
-        <v>407</v>
+        <v>519</v>
       </c>
       <c r="L65" s="638"/>
       <c r="M65" s="53"/>
@@ -19032,7 +19826,7 @@
     </row>
     <row r="67" spans="1:23" customHeight="1" ht="28.5">
       <c r="A67" s="634" t="s">
-        <v>408</v>
+        <v>520</v>
       </c>
       <c r="B67" s="635"/>
       <c r="C67" s="635"/>
@@ -19053,7 +19847,7 @@
       <c r="C68" s="61"/>
       <c r="D68" s="61"/>
       <c r="E68" s="631" t="s">
-        <v>409</v>
+        <v>521</v>
       </c>
       <c r="F68" s="632"/>
       <c r="G68" s="632"/>
@@ -19069,7 +19863,7 @@
       <c r="C69" s="199"/>
       <c r="D69" s="199"/>
       <c r="E69" s="628" t="s">
-        <v>410</v>
+        <v>522</v>
       </c>
       <c r="F69" s="629"/>
       <c r="G69" s="629"/>
@@ -19097,7 +19891,7 @@
     </row>
     <row r="71" spans="1:23" customHeight="1" ht="10.5">
       <c r="A71" s="627" t="s">
-        <v>411</v>
+        <v>523</v>
       </c>
       <c r="B71" s="627"/>
       <c r="C71" s="627"/>
@@ -19790,45 +20584,45 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>412</v>
+        <v>524</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>413</v>
+        <v>525</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>414</v>
+        <v>526</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>415</v>
+        <v>527</v>
       </c>
       <c r="B2" t="s">
-        <v>416</v>
+        <v>528</v>
       </c>
       <c r="C2" t="s">
-        <v>417</v>
+        <v>529</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>418</v>
+        <v>530</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>419</v>
+        <v>531</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="B4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="B5" t="s">
-        <v>420</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>
